--- a/data/VAKFA (TRY).xlsx
+++ b/data/VAKFA (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K39"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -415,6 +415,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,30 +423,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -459,30 +463,33 @@
         <v xml:space="preserve">    Nakit, Nakit Benzerleri ve Merkez Bankası</v>
       </c>
       <c r="B3">
+        <v>184568000</v>
+      </c>
+      <c r="C3">
         <v>97569000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>197394000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>384598000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>306833000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>745298000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>510523000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1794960000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>174993000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>95321000</v>
       </c>
     </row>
@@ -491,30 +498,33 @@
         <v xml:space="preserve">    İtfa Edilmiş Maliyet ile Ölçülen Finansal Varlıklar (Net)</v>
       </c>
       <c r="B4">
+        <v>34796434000</v>
+      </c>
+      <c r="C4">
         <v>41713384000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>29833081000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>31839448000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>32424129000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>39078584000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>37481289000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>25025122000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>22611298000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>7008665000</v>
       </c>
     </row>
@@ -525,10 +535,13 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>0</v>
       </c>
     </row>
@@ -537,30 +550,33 @@
         <v xml:space="preserve">    Faktoring Alacakları</v>
       </c>
       <c r="B6">
+        <v>34796434000</v>
+      </c>
+      <c r="C6">
         <v>41713384000</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>29833081000</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>31839448000</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>32424129000</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>39078584000</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>37455124000</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>24983259000</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>22611298000</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>7006937000</v>
       </c>
     </row>
@@ -569,30 +585,33 @@
         <v xml:space="preserve">    Takipteki Alacaklar</v>
       </c>
       <c r="B7">
+        <v>97282000</v>
+      </c>
+      <c r="C7">
         <v>97366000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>97461000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>97579000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>97810000</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>98609000</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>99074000</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>103050000</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>52363000</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>66879000</v>
       </c>
     </row>
@@ -601,30 +620,33 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları / Özel Karşılıklar (-)</v>
       </c>
       <c r="B8">
+        <v>-97282000</v>
+      </c>
+      <c r="C8">
         <v>-97366000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-97461000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>-97579000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>-97810000</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>-98609000</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>-72909000</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>-61187000</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>-52363000</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>-65151000</v>
       </c>
     </row>
@@ -659,36 +681,42 @@
       <c r="J9">
         <v>0</v>
       </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Maddi Duran Varlıklar (Net)</v>
       </c>
       <c r="B10">
+        <v>7573000</v>
+      </c>
+      <c r="C10">
         <v>10336000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>13518000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>15444000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>19308000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>18369000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>8278000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>3053000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>4027000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>2558000</v>
       </c>
     </row>
@@ -697,30 +725,33 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar (Net)</v>
       </c>
       <c r="B11">
+        <v>1978000</v>
+      </c>
+      <c r="C11">
         <v>1091000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>705000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>867000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>1053000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>847000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>997000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1496000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1856000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>2069000</v>
       </c>
     </row>
@@ -755,6 +786,9 @@
       <c r="J12">
         <v>0</v>
       </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -773,18 +807,21 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>7524000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1487000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1028000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>203000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>158000</v>
       </c>
     </row>
@@ -793,30 +830,33 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B14">
+        <v>37140000</v>
+      </c>
+      <c r="C14">
         <v>29561000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>21236000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>21275000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>20506000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>4160000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>946000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>547000</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>51219000</v>
       </c>
     </row>
@@ -825,30 +865,33 @@
         <v xml:space="preserve">    Diğer Aktifler</v>
       </c>
       <c r="B15">
+        <v>42198000</v>
+      </c>
+      <c r="C15">
         <v>37046000</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>80528000</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>59020000</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>67043000</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>125285000</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>190464000</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>411474000</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>182856000</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>11080000</v>
       </c>
     </row>
@@ -857,30 +900,33 @@
         <v xml:space="preserve">    (ARA TOPLAM) 1</v>
       </c>
       <c r="B16">
+        <v>35069891000</v>
+      </c>
+      <c r="C16">
         <v>41888987000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>30146462000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>32377455000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>32888590000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>40021854000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>38235771000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>27263871000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>23001424000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>7179227000</v>
       </c>
     </row>
@@ -915,36 +961,42 @@
       <c r="J17">
         <v>220000</v>
       </c>
+      <c r="K17">
+        <v>220000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v xml:space="preserve">    TOPLAM VARLIKLAR</v>
       </c>
       <c r="B18">
+        <v>35070111000</v>
+      </c>
+      <c r="C18">
         <v>41889207000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>30146682000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>32377675000</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>32888810000</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>40022074000</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>38235991000</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>27264091000</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>23001644000</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>7179447000</v>
       </c>
     </row>
@@ -953,30 +1005,33 @@
         <v xml:space="preserve">    YÜKÜMLÜLÜKLER TOPLAMI</v>
       </c>
       <c r="B19">
+        <v>27693479000</v>
+      </c>
+      <c r="C19">
         <v>34880244000</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>24340834000</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>27098201000</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>28497715000</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>36470647000</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>35562528000</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>25478691000</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>21847344000</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>6588773000</v>
       </c>
     </row>
@@ -985,30 +1040,33 @@
         <v xml:space="preserve">    Alınan Krediler</v>
       </c>
       <c r="B20">
+        <v>27301272000</v>
+      </c>
+      <c r="C20">
         <v>34499576000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>23578599000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>26142311000</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>28141846000</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>36099092000</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>33000633000</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>23406668000</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>20158989000</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>5483580000</v>
       </c>
     </row>
@@ -1017,30 +1075,33 @@
         <v xml:space="preserve">    Faktoring Borçları</v>
       </c>
       <c r="B21">
+        <v>2131000</v>
+      </c>
+      <c r="C21">
         <v>11000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>5965000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>10000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>376000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>2142000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>90000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1955000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>5468000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>7309000</v>
       </c>
     </row>
@@ -1075,36 +1136,42 @@
       <c r="J22">
         <v>0</v>
       </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlar</v>
       </c>
       <c r="B23">
+        <v>7113000</v>
+      </c>
+      <c r="C23">
         <v>10282000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>13442000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>15113000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>17994000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>17243000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>6497000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>539000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>890000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>2361000</v>
       </c>
     </row>
@@ -1116,27 +1183,30 @@
         <v>0</v>
       </c>
       <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
         <v>402867000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>640415000</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>2228522000</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>1310605000</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1513520000</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>767915000</v>
       </c>
     </row>
@@ -1145,30 +1215,33 @@
         <v xml:space="preserve">    Karşılıklar</v>
       </c>
       <c r="B25">
+        <v>124151000</v>
+      </c>
+      <c r="C25">
         <v>98350000</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>69966000</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>70226000</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>68285000</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>82865000</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>73500000</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>61343000</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>46847000</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>33424000</v>
       </c>
     </row>
@@ -1177,30 +1250,33 @@
         <v xml:space="preserve">    Cari Vergi Borcu</v>
       </c>
       <c r="B26">
+        <v>246783000</v>
+      </c>
+      <c r="C26">
         <v>253665000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>257332000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>225673000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>258406000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>265917000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>231124000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>155346000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>96482000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>70271000</v>
       </c>
     </row>
@@ -1230,9 +1306,12 @@
         <v>0</v>
       </c>
       <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>137000</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>0</v>
       </c>
     </row>
@@ -1241,30 +1320,33 @@
         <v xml:space="preserve">    Diğer Yükümlülükler</v>
       </c>
       <c r="B28">
+        <v>12029000</v>
+      </c>
+      <c r="C28">
         <v>18360000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>12663000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>4453000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>10808000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>3388000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>22162000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>542235000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>25011000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>2851000</v>
       </c>
     </row>
@@ -1273,30 +1355,33 @@
         <v xml:space="preserve">    (ARA TOPLAM) 2</v>
       </c>
       <c r="B29">
+        <v>27693479000</v>
+      </c>
+      <c r="C29">
         <v>34880244000</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>24340834000</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>27098201000</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>28497715000</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>36470647000</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>35562528000</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>25478691000</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>21847344000</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>6588773000</v>
       </c>
     </row>
@@ -1331,36 +1416,42 @@
       <c r="J30">
         <v>0</v>
       </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v xml:space="preserve">    ÖZKAYNAKLAR</v>
       </c>
       <c r="B31">
+        <v>7376632000</v>
+      </c>
+      <c r="C31">
         <v>7008963000</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>5805848000</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>5279474000</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>4391095000</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>3551427000</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>2673463000</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>1785400000</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>1154300000</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>590674000</v>
       </c>
     </row>
@@ -1372,7 +1463,7 @@
         <v>900000000</v>
       </c>
       <c r="C32">
-        <v>850000000</v>
+        <v>900000000</v>
       </c>
       <c r="D32">
         <v>850000000</v>
@@ -1387,12 +1478,15 @@
         <v>850000000</v>
       </c>
       <c r="H32">
-        <v>450000000</v>
+        <v>850000000</v>
       </c>
       <c r="I32">
         <v>450000000</v>
       </c>
       <c r="J32">
+        <v>450000000</v>
+      </c>
+      <c r="K32">
         <v>350000000</v>
       </c>
     </row>
@@ -1407,24 +1501,27 @@
         <v>51000</v>
       </c>
       <c r="D33">
+        <v>51000</v>
+      </c>
+      <c r="E33">
         <v>54466000</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>47381000</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>39450000</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>36928000</v>
-      </c>
-      <c r="H33">
-        <v>22501000</v>
       </c>
       <c r="I33">
         <v>22501000</v>
       </c>
       <c r="J33">
+        <v>22501000</v>
+      </c>
+      <c r="K33">
         <v>5595000</v>
       </c>
     </row>
@@ -1439,24 +1536,27 @@
         <v>3496807000</v>
       </c>
       <c r="D34">
+        <v>3496807000</v>
+      </c>
+      <c r="E34">
         <v>3493714000</v>
-      </c>
-      <c r="E34">
-        <v>1786535000</v>
       </c>
       <c r="F34">
         <v>1786535000</v>
       </c>
       <c r="G34">
+        <v>1786535000</v>
+      </c>
+      <c r="H34">
         <v>281799000</v>
-      </c>
-      <c r="H34">
-        <v>135079000</v>
       </c>
       <c r="I34">
         <v>135079000</v>
       </c>
       <c r="J34">
+        <v>135079000</v>
+      </c>
+      <c r="K34">
         <v>118793000</v>
       </c>
     </row>
@@ -1465,24 +1565,27 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar veya Zararı</v>
       </c>
       <c r="B35">
-        <v>44237000</v>
+        <v>1969095000</v>
       </c>
       <c r="C35">
         <v>44237000</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="G35">
+      <c r="D35">
+        <v>44237000</v>
+      </c>
+      <c r="F35">
         <v>0</v>
       </c>
       <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
         <v>546720000</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
       <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
         <v>0</v>
       </c>
     </row>
@@ -1491,30 +1594,33 @@
         <v xml:space="preserve">    Dönem Net Karı veya Zararı</v>
       </c>
       <c r="B36">
+        <v>461585000</v>
+      </c>
+      <c r="C36">
         <v>1924858000</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>1414753000</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>881294000</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>1707179000</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>875442000</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>1504736000</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>631100000</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>546720000</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>116286000</v>
       </c>
     </row>
@@ -1522,10 +1628,10 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Kontrol Gücü Olmayan Paylar</v>
       </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="E37">
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="F37">
         <v>0</v>
       </c>
     </row>
@@ -1534,30 +1640,33 @@
         <v xml:space="preserve">    TOPLAM KAYNAKLAR</v>
       </c>
       <c r="B38">
+        <v>35070111000</v>
+      </c>
+      <c r="C38">
         <v>41889207000</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>30146682000</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>32377675000</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>32888810000</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>40022074000</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>38235991000</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>27264091000</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>23001644000</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>7179447000</v>
       </c>
     </row>
@@ -1568,14 +1677,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:Q30"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1593,6 +1702,7 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1600,48 +1710,51 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2022/3</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -1655,48 +1768,51 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>1852213000</v>
+      </c>
+      <c r="C3">
         <v>9574437000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>7255446000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>4926193000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>2653970000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>12809590000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>10280627000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>6918423000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3225693000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>8670672000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>3095297000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1319228000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2429221000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>725811000</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>315929000</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>772176000</v>
       </c>
     </row>
@@ -1705,48 +1821,51 @@
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
       <c r="B4">
+        <v>1852213000</v>
+      </c>
+      <c r="C4">
         <v>9574437000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>7255446000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>4926193000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2653970000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>12809590000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>10280627000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>6918423000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>3225693000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>8670672000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>3095297000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1319228000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>2429221000</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>725811000</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>315929000</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>772176000</v>
       </c>
     </row>
@@ -1776,9 +1895,6 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1807,6 +1923,9 @@
         <v>0</v>
       </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>0</v>
       </c>
     </row>
@@ -1826,9 +1945,6 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1857,6 +1973,9 @@
         <v>0</v>
       </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>0</v>
       </c>
     </row>
@@ -1909,54 +2028,60 @@
       <c r="P9">
         <v>0</v>
       </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-1082616000</v>
+      </c>
+      <c r="C10">
         <v>-6587793000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-5115079000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-3563914000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-2006492000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-10455033000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-8594106000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-5735250000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-2770469000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-6510345000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-2257442000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-977003000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>-1692690000</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>-532733000</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>-238125000</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>-603973000</v>
       </c>
     </row>
@@ -1965,48 +2090,51 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>769597000</v>
+      </c>
+      <c r="C11">
         <v>2986644000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>2140367000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>1362279000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>647478000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>2354557000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1686521000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1183173000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>455224000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>2160327000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>837855000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>342225000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>736531000</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>193078000</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>77804000</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>168203000</v>
       </c>
     </row>
@@ -2015,48 +2143,51 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-91735000</v>
+      </c>
+      <c r="C12">
         <v>-336575000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-229534000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-145518000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-60347000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>-230783000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-147628000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-89465000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-41351000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-133733000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-45145000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-18901000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>-59165000</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>-20493000</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>-9029000</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>-31036000</v>
       </c>
     </row>
@@ -2065,48 +2196,51 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>677862000</v>
+      </c>
+      <c r="C13">
         <v>2650069000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>1910833000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1216761000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>587131000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>2123774000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1538893000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1093708000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>413873000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>2026594000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>792710000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>323324000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>677366000</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>172585000</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>68775000</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>137167000</v>
       </c>
     </row>
@@ -2115,48 +2249,51 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>977354000</v>
+      </c>
+      <c r="C14">
         <v>3497681000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>2925765000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>2298926000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>1014111000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1945553000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1413539000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>762742000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>532667000</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>1857587000</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1038385000</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>172696000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>1286478000</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>917044000</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>575666000</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>1141711000</v>
       </c>
     </row>
@@ -2165,11 +2302,11 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-23950000</v>
+      </c>
+      <c r="C15">
         <v>-26650000</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
       <c r="D15">
         <v>0</v>
       </c>
@@ -2177,36 +2314,39 @@
         <v>0</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>-79615000</v>
-      </c>
-      <c r="G15">
-        <v>-26165000</v>
       </c>
       <c r="H15">
         <v>-26165000</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>-26165000</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>-26165000</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>-10467000</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
       <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>-7440000</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>-1972000</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>-71000</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>-8861000</v>
       </c>
     </row>
@@ -2215,48 +2355,51 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-971517000</v>
+      </c>
+      <c r="C16">
         <v>-3372971000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-2817557000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-2256025000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-996619000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-1549037000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-1132981000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-578747000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-457826000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-1709507000</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-980135000</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-145818000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>-1233939000</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>-877718000</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>-540279000</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>-1109218000</v>
       </c>
     </row>
@@ -2265,48 +2408,51 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>659749000</v>
+      </c>
+      <c r="C17">
         <v>2748129000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>2019041000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>1259662000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>604623000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>2440675000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1793286000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>1251538000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>488714000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>2148509000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>840493000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>350202000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>722465000</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>209939000</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>104091000</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>160799000</v>
       </c>
     </row>
@@ -2323,13 +2469,13 @@
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="E18">
         <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="J18">
+      <c r="H18">
         <v>0</v>
       </c>
       <c r="K18">
@@ -2348,6 +2494,9 @@
         <v>0</v>
       </c>
       <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
         <v>0</v>
       </c>
     </row>
@@ -2364,13 +2513,13 @@
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="F19">
+      <c r="E19">
         <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
-      <c r="J19">
+      <c r="H19">
         <v>0</v>
       </c>
       <c r="K19">
@@ -2389,6 +2538,9 @@
         <v>0</v>
       </c>
       <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <v>0</v>
       </c>
     </row>
@@ -2405,13 +2557,13 @@
       <c r="D20">
         <v>0</v>
       </c>
-      <c r="F20">
+      <c r="E20">
         <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="J20">
+      <c r="H20">
         <v>0</v>
       </c>
       <c r="K20">
@@ -2430,6 +2582,9 @@
         <v>0</v>
       </c>
       <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <v>0</v>
       </c>
     </row>
@@ -2438,48 +2593,51 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>659749000</v>
+      </c>
+      <c r="C21">
         <v>2748129000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2019041000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1259662000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>604623000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>2440675000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>1793286000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1251538000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>488714000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>2148509000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>840493000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>350202000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>722465000</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>209939000</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>104091000</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>160799000</v>
       </c>
     </row>
@@ -2488,48 +2646,51 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-198164000</v>
+      </c>
+      <c r="C22">
         <v>-823271000</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-604288000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-378368000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-181606000</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>-733496000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-538939000</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-376096000</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>-146949000</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>-643773000</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>-209393000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-86797000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>-175745000</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>-50255000</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>-50729000</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>-44513000</v>
       </c>
     </row>
@@ -2538,48 +2699,51 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-205743000</v>
+      </c>
+      <c r="C23">
         <v>-832326000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-605018000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-379137000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-181691000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-750535000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-539652000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-376788000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-146931000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>-646026000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>-210077000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-87100000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>-125516000</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <v>-96064000</v>
       </c>
     </row>
@@ -2614,24 +2778,27 @@
         <v>0</v>
       </c>
       <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>-18000</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>-50229000</v>
-      </c>
-      <c r="N25">
-        <v>-50255000</v>
       </c>
       <c r="O25">
         <v>-50255000</v>
       </c>
       <c r="P25">
+        <v>-50255000</v>
+      </c>
+      <c r="Q25">
         <v>0</v>
       </c>
     </row>
@@ -2640,48 +2807,51 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>461585000</v>
+      </c>
+      <c r="C26">
         <v>1924858000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>1414753000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>881294000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>423017000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1707179000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>1254347000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>875442000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>341765000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>1504736000</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>631100000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>263405000</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>546720000</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>159684000</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>53362000</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>116286000</v>
       </c>
     </row>
@@ -2698,13 +2868,13 @@
       <c r="D27">
         <v>0</v>
       </c>
-      <c r="F27">
+      <c r="E27">
         <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
-      <c r="J27">
+      <c r="H27">
         <v>0</v>
       </c>
       <c r="K27">
@@ -2723,6 +2893,9 @@
         <v>0</v>
       </c>
       <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <v>0</v>
       </c>
     </row>
@@ -2731,48 +2904,51 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>461585000</v>
+      </c>
+      <c r="C28">
         <v>1924858000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1414753000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>881294000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>423017000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>1707179000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>1254347000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>875442000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>341765000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>1504736000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>631100000</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>263405000</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>546720000</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>159684000</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>53362000</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>116286000</v>
       </c>
     </row>
@@ -2789,13 +2965,16 @@
       <c r="D29">
         <v>0</v>
       </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
-      <c r="J29">
+      <c r="H29">
         <v>0</v>
       </c>
       <c r="K29">
@@ -2814,6 +2993,9 @@
         <v>0</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>0</v>
       </c>
     </row>
@@ -2822,61 +3004,64 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>461585000</v>
+      </c>
+      <c r="C30">
         <v>1924858000</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1414753000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>881294000</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>423017000</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>1707179000</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1254347000</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>875442000</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>341765000</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1504736000</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>631100000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>263405000</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>546720000</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>159684000</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>53362000</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>116286000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:Q30"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2894,6 +3079,7 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2901,48 +3087,51 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2022/3</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -2956,39 +3145,42 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>1852213000</v>
+      </c>
+      <c r="C3">
         <v>2318991000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>2329253000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2272223000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>2653970000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2528963000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>3362204000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>3692730000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3225693000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1776069000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1319228000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>409882000</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>315929000</v>
       </c>
     </row>
@@ -2997,39 +3189,42 @@
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
       <c r="B4">
+        <v>1852213000</v>
+      </c>
+      <c r="C4">
         <v>2318991000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2329253000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2272223000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2653970000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>2528963000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>3362204000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>3692730000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>3225693000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>1776069000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1319228000</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>409882000</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>315929000</v>
       </c>
     </row>
@@ -3056,12 +3251,6 @@
       <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -3071,16 +3260,19 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="J7">
         <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="N7">
+      <c r="M7">
         <v>0</v>
       </c>
       <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>0</v>
       </c>
     </row>
@@ -3097,12 +3289,6 @@
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -3112,16 +3298,19 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="J8">
         <v>0</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="N8">
+      <c r="M8">
         <v>0</v>
       </c>
       <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>0</v>
       </c>
     </row>
@@ -3153,16 +3342,19 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="J9">
         <v>0</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
-      <c r="N9">
+      <c r="M9">
         <v>0</v>
       </c>
       <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>0</v>
       </c>
     </row>
@@ -3171,39 +3363,42 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-1082616000</v>
+      </c>
+      <c r="C10">
         <v>-1472714000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-1551165000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-1557422000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-2006492000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-1860927000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-2858856000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-2964781000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-2770469000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-1280439000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-977003000</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>-294608000</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>-238125000</v>
       </c>
     </row>
@@ -3212,39 +3407,42 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>769597000</v>
+      </c>
+      <c r="C11">
         <v>846277000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>778088000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>714801000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>647478000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>668036000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>503348000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>727949000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>455224000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>495630000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>342225000</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>115274000</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>77804000</v>
       </c>
     </row>
@@ -3253,39 +3451,42 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-91735000</v>
+      </c>
+      <c r="C12">
         <v>-107041000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-84016000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-85171000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-60347000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>-83155000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-58163000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-48114000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-41351000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-26244000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-18901000</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>-11464000</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>-9029000</v>
       </c>
     </row>
@@ -3294,39 +3495,42 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>677862000</v>
+      </c>
+      <c r="C13">
         <v>739236000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>694072000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>629630000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>587131000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>584881000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>445185000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>679835000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>413873000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>469386000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>323324000</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>103810000</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>68775000</v>
       </c>
     </row>
@@ -3335,39 +3539,42 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>977354000</v>
+      </c>
+      <c r="C14">
         <v>571916000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>626839000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>1284815000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>1014111000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>532014000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>650797000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>230075000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>532667000</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>865689000</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>172696000</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>341378000</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>575666000</v>
       </c>
     </row>
@@ -3376,11 +3583,11 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-23950000</v>
+      </c>
+      <c r="C15">
         <v>-26650000</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
       <c r="D15">
         <v>0</v>
       </c>
@@ -3388,27 +3595,30 @@
         <v>0</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>-53450000</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>-26165000</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="K15">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>-10467000</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="N15">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>-1901000</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>-71000</v>
       </c>
     </row>
@@ -3417,39 +3627,42 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-971517000</v>
+      </c>
+      <c r="C16">
         <v>-555414000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-561532000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-1259406000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-996619000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-416056000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-554234000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-120921000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-457826000</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-834317000</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-145818000</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>-337439000</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>-540279000</v>
       </c>
     </row>
@@ -3458,39 +3671,42 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>659749000</v>
+      </c>
+      <c r="C17">
         <v>729088000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>759379000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>655039000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>604623000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>647389000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>541748000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>762824000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>488714000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>490291000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>350202000</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>105848000</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>104091000</v>
       </c>
     </row>
@@ -3504,19 +3720,22 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="K18">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="N18">
+      <c r="M18">
         <v>0</v>
       </c>
       <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
         <v>0</v>
       </c>
     </row>
@@ -3530,19 +3749,22 @@
       <c r="C19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="K19">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>0</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="N19">
+      <c r="M19">
         <v>0</v>
       </c>
       <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>0</v>
       </c>
     </row>
@@ -3556,19 +3778,22 @@
       <c r="C20">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="K20">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="N20">
+      <c r="M20">
         <v>0</v>
       </c>
       <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>0</v>
       </c>
     </row>
@@ -3577,39 +3802,42 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>659749000</v>
+      </c>
+      <c r="C21">
         <v>729088000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>759379000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>655039000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>604623000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>647389000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>541748000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>762824000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>488714000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>490291000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>350202000</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>105848000</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>104091000</v>
       </c>
     </row>
@@ -3618,39 +3846,42 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-198164000</v>
+      </c>
+      <c r="C22">
         <v>-218983000</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-225920000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-196762000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-181606000</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>-194557000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-162843000</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-229147000</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>-146949000</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>-122596000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-86797000</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>474000</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>-50729000</v>
       </c>
     </row>
@@ -3659,39 +3890,42 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-205743000</v>
+      </c>
+      <c r="C23">
         <v>-227308000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-225881000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-197446000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-181691000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-210883000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-162864000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-229857000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-146931000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>-122977000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-87100000</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
       <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
         <v>0</v>
       </c>
     </row>
@@ -3723,21 +3957,24 @@
         <v>0</v>
       </c>
       <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>18000</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>-18000</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
       <c r="L25">
         <v>0</v>
       </c>
-      <c r="N25">
+      <c r="M25">
         <v>0</v>
       </c>
       <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
         <v>-50255000</v>
       </c>
     </row>
@@ -3746,39 +3983,42 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>461585000</v>
+      </c>
+      <c r="C26">
         <v>510105000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>533459000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>458277000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>423017000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>452832000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>378905000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>533677000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>341765000</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>367695000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>263405000</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>106322000</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>53362000</v>
       </c>
     </row>
@@ -3792,19 +4032,22 @@
       <c r="C27">
         <v>0</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="K27">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>0</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
-      <c r="N27">
+      <c r="M27">
         <v>0</v>
       </c>
       <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>0</v>
       </c>
     </row>
@@ -3813,39 +4056,42 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>461585000</v>
+      </c>
+      <c r="C28">
         <v>510105000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>533459000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>458277000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>423017000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>452832000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>378905000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>533677000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>341765000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>367695000</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>263405000</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>106322000</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>53362000</v>
       </c>
     </row>
@@ -3859,19 +4105,28 @@
       <c r="C29">
         <v>0</v>
       </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="G29">
         <v>0</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
-      <c r="N29">
+      <c r="M29">
         <v>0</v>
       </c>
       <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>0</v>
       </c>
     </row>
@@ -3880,52 +4135,55 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>461585000</v>
+      </c>
+      <c r="C30">
         <v>510105000</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>533459000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>458277000</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>423017000</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>452832000</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>378905000</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>533677000</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>341765000</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>367695000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>263405000</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>106322000</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>53362000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:Q30"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3943,6 +4201,7 @@
     <col min="14" max="14" customWidth="1" width="20"/>
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
+    <col min="17" max="17" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3950,48 +4209,51 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2022/3</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -4005,39 +4267,42 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>8772680000</v>
+      </c>
+      <c r="C3">
         <v>9574437000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>9784409000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>10817360000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>12237867000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>12809590000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>12493798000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>10577137000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>8670672000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>4798707000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>3432520000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2429221000</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>772176000</v>
       </c>
     </row>
@@ -4046,39 +4311,42 @@
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
       <c r="B4">
+        <v>8772680000</v>
+      </c>
+      <c r="C4">
         <v>9574437000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9784409000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>10817360000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>12237867000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>12809590000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>12493798000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>10577137000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>8670672000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>4798707000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>3432520000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>2429221000</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>772176000</v>
       </c>
     </row>
@@ -4096,9 +4364,6 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Finansman Kredilerinden Gelirler</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -4108,10 +4373,7 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7">
         <v>0</v>
       </c>
       <c r="I7">
@@ -4129,7 +4391,10 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="P7">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>0</v>
       </c>
     </row>
@@ -4137,9 +4402,6 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Kiralama Gelirleri</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
       <c r="C8">
         <v>0</v>
       </c>
@@ -4149,10 +4411,7 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="G8">
         <v>0</v>
       </c>
       <c r="I8">
@@ -4170,7 +4429,10 @@
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="P8">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>0</v>
       </c>
     </row>
@@ -4193,7 +4455,7 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="H9">
+      <c r="G9">
         <v>0</v>
       </c>
       <c r="I9">
@@ -4211,7 +4473,10 @@
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="P9">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>0</v>
       </c>
     </row>
@@ -4220,39 +4485,42 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-5663917000</v>
+      </c>
+      <c r="C10">
         <v>-6587793000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-6976006000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-8283697000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-9691056000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-10455033000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-9988153000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-8303811000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-6510345000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-3417399000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-2431568000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>-1692690000</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>-603973000</v>
       </c>
     </row>
@@ -4261,39 +4529,42 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>3108763000</v>
+      </c>
+      <c r="C11">
         <v>2986644000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>2808403000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>2533663000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>2546811000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>2354557000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>2505645000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>2273326000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>2160327000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1381308000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1000952000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>736531000</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>168203000</v>
       </c>
     </row>
@@ -4302,39 +4573,42 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-367963000</v>
+      </c>
+      <c r="C12">
         <v>-336575000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-312689000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-286836000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-249779000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>-230783000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-178053000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-156183000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-133733000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-83817000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-69037000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>-59165000</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>-31036000</v>
       </c>
     </row>
@@ -4343,39 +4617,42 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>2740800000</v>
+      </c>
+      <c r="C13">
         <v>2650069000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>2495714000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>2246827000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>2297032000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>2123774000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>2327592000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>2117143000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>2026594000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>1297491000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>931915000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>677366000</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>137167000</v>
       </c>
     </row>
@@ -4384,39 +4661,42 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>3460924000</v>
+      </c>
+      <c r="C14">
         <v>3497681000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>3457779000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>3481737000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>2426997000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1945553000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1581944000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>2217558000</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>1857587000</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1407819000</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>883508000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>1286478000</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>1141711000</v>
       </c>
     </row>
@@ -4425,39 +4705,42 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-50600000</v>
+      </c>
+      <c r="C15">
         <v>-26650000</v>
-      </c>
-      <c r="C15">
-        <v>-53450000</v>
       </c>
       <c r="D15">
         <v>-53450000</v>
       </c>
       <c r="E15">
-        <v>-79615000</v>
+        <v>-53450000</v>
       </c>
       <c r="F15">
         <v>-79615000</v>
       </c>
-      <c r="H15">
+      <c r="G15">
+        <v>-79615000</v>
+      </c>
+      <c r="I15">
         <v>-41863000</v>
-      </c>
-      <c r="I15">
-        <v>-26165000</v>
       </c>
       <c r="J15">
         <v>-26165000</v>
       </c>
       <c r="K15">
+        <v>-26165000</v>
+      </c>
+      <c r="L15">
         <v>-15935000</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>-7369000</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>-7440000</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>-8861000</v>
       </c>
     </row>
@@ -4466,39 +4749,42 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-3347869000</v>
+      </c>
+      <c r="C16">
         <v>-3372971000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-3233613000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-3226315000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-2087830000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-1549037000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-1308119000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-2021515000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-1709507000</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-1336356000</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-839478000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>-1233939000</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>-1109218000</v>
       </c>
     </row>
@@ -4507,39 +4793,42 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>2803255000</v>
+      </c>
+      <c r="C17">
         <v>2748129000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>2666430000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>2448799000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>2556584000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>2440675000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>2559554000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>2287021000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>2148509000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1353019000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>968576000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>722465000</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>160799000</v>
       </c>
     </row>
@@ -4547,16 +4836,13 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="J18">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>0</v>
       </c>
       <c r="K18">
@@ -4568,7 +4854,10 @@
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="P18">
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
         <v>0</v>
       </c>
     </row>
@@ -4576,16 +4865,13 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar)</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
       <c r="C19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="J19">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>0</v>
       </c>
       <c r="K19">
@@ -4597,7 +4883,10 @@
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="P19">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <v>0</v>
       </c>
     </row>
@@ -4605,16 +4894,13 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
       <c r="C20">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="J20">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>0</v>
       </c>
       <c r="K20">
@@ -4626,7 +4912,10 @@
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="P20">
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <v>0</v>
       </c>
     </row>
@@ -4635,39 +4924,42 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>2803255000</v>
+      </c>
+      <c r="C21">
         <v>2748129000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2666430000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>2448799000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>2556584000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>2440675000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>2559554000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>2287021000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>2148509000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>1353019000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>968576000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>722465000</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>160799000</v>
       </c>
     </row>
@@ -4676,39 +4968,42 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-839829000</v>
+      </c>
+      <c r="C22">
         <v>-823271000</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-798845000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-735768000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-768153000</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>-733496000</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-810476000</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>-703925000</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>-643773000</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>-334883000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-211813000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>-175745000</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>-44513000</v>
       </c>
     </row>
@@ -4717,39 +5012,42 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-856378000</v>
+      </c>
+      <c r="C23">
         <v>-832326000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-815901000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-752884000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-785295000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-750535000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-812737000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-705857000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>-646026000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>-335593000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-212616000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>-125516000</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>-96064000</v>
       </c>
     </row>
@@ -4772,21 +5070,24 @@
         <v>0</v>
       </c>
       <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>18000</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>26000</v>
+      <c r="G25">
+        <v>0</v>
       </c>
       <c r="L25">
         <v>26000</v>
       </c>
       <c r="M25">
+        <v>26000</v>
+      </c>
+      <c r="N25">
         <v>-50229000</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>0</v>
       </c>
     </row>
@@ -4795,39 +5096,42 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>1963426000</v>
+      </c>
+      <c r="C26">
         <v>1924858000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>1867585000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1713031000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>1788431000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1707179000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>1749078000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>1583096000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>1504736000</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>1018136000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>756763000</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>546720000</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>116286000</v>
       </c>
     </row>
@@ -4835,16 +5139,13 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Net Karı (Zararı)</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
       <c r="C27">
         <v>0</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>0</v>
       </c>
       <c r="K27">
@@ -4856,7 +5157,10 @@
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="P27">
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <v>0</v>
       </c>
     </row>
@@ -4865,39 +5169,42 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>1963426000</v>
+      </c>
+      <c r="C28">
         <v>1924858000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1867585000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>1713031000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>1788431000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>1707179000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>1749078000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1583096000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>1504736000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>1018136000</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>756763000</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>546720000</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>116286000</v>
       </c>
     </row>
@@ -4911,10 +5218,10 @@
       <c r="C29">
         <v>0</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="J29">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>0</v>
       </c>
       <c r="K29">
@@ -4926,7 +5233,10 @@
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="P29">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>0</v>
       </c>
     </row>
@@ -4935,52 +5245,55 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>1963426000</v>
+      </c>
+      <c r="C30">
         <v>1924858000</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1867585000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1713031000</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>1788431000</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>1707179000</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>1749078000</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1583096000</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1504736000</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>1018136000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>756763000</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>546720000</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>116286000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:N45"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4994,6 +5307,8 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5001,36 +5316,42 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -5044,36 +5365,42 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>-179034000</v>
+      </c>
+      <c r="C3">
         <v>2180215000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>621040000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>490067000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
+        <v>-451646000</v>
+      </c>
+      <c r="G3">
         <v>1115003000</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1463179000</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2203262000</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>1881309000</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>945675000</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>263233000</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>-112745000</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>187010000</v>
       </c>
     </row>
@@ -5082,36 +5409,42 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>1637061000</v>
+      </c>
+      <c r="C4">
         <v>9565696000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>6763998000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>4622136000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
+        <v>1952588000</v>
+      </c>
+      <c r="G4">
         <v>12952560000</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>10134816000</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>6793144000</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>6814870000</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>2727731000</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>2226469000</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>718367000</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>570734000</v>
       </c>
     </row>
@@ -5120,36 +5453,42 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-1525646000</v>
+      </c>
+      <c r="C5">
         <v>-6282796000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-5346945000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>-3617110000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>-2352937000</v>
+      </c>
+      <c r="G5">
         <v>-10948614000</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>-8006534000</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>-4203467000</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>-5474956000</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>-1994450000</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>-1588750000</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>-563308000</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>-515777000</v>
       </c>
     </row>
@@ -5157,13 +5496,19 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
     </row>
@@ -5172,36 +5517,42 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>2164000</v>
+      </c>
+      <c r="C7">
         <v>10829000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>8916000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>6074000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
+        <v>2545000</v>
+      </c>
+      <c r="G7">
         <v>21825000</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>17987000</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>11284000</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>1164455000</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>410691000</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>21394000</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>3653000</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>2811000</v>
       </c>
     </row>
@@ -5210,36 +5561,42 @@
         <v xml:space="preserve">    Zarar Olarak Muhasebeleştirilen Takipteki Alacaklardan Tahsilatlar</v>
       </c>
       <c r="B8">
+        <v>84000</v>
+      </c>
+      <c r="C8">
         <v>444000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>349000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>213000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>213000</v>
+      </c>
+      <c r="G8">
         <v>1264000</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>948000</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>465000</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>-5619000</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>1643000</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>-7088000</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>4176000</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>6641000</v>
       </c>
     </row>
@@ -5248,36 +5605,42 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-60360000</v>
+      </c>
+      <c r="C9">
         <v>-195929000</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-146095000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>-96959000</v>
       </c>
-      <c r="E9">
+      <c r="F9">
+        <v>-43874000</v>
+      </c>
+      <c r="G9">
         <v>-137475000</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>-101599000</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>-66213000</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>-68722000</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>-27669000</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>-31141000</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-16511000</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-31036000</v>
       </c>
     </row>
@@ -5286,36 +5649,42 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-224950000</v>
+      </c>
+      <c r="C10">
         <v>-814443000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-596191000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-388758000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
+        <v>-2314000</v>
+      </c>
+      <c r="G10">
         <v>-722637000</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-555957000</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-326100000</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-539203000</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-159446000</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-116124000</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-62954000</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-33110000</v>
       </c>
     </row>
@@ -5324,36 +5693,42 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-7387000</v>
+      </c>
+      <c r="C11">
         <v>-103586000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-62992000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>-35529000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
+        <v>-7867000</v>
+      </c>
+      <c r="G11">
         <v>-51920000</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>-26482000</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>-5851000</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>-9516000</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>-12825000</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>-241527000</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>-196168000</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>179882000</v>
       </c>
     </row>
@@ -5362,36 +5737,42 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>360276000</v>
+      </c>
+      <c r="C12">
         <v>-3138957000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-1153976000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-1052033000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
+        <v>643923000</v>
+      </c>
+      <c r="G12">
         <v>-1420185000</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-1062274000</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-1852227000</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-2181983000</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>821579000</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-872395000</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>376075000</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>-172940000</v>
       </c>
     </row>
@@ -5400,36 +5781,42 @@
         <v xml:space="preserve">    Faktoring Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B13">
+        <v>7111471000</v>
+      </c>
+      <c r="C13">
         <v>-9201164000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>3177057000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>928345000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
+        <v>12279739000</v>
+      </c>
+      <c r="G13">
         <v>5197100000</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>10893193000</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>-1332376000</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>-14097533000</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>-2473656000</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>-15425263000</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>-2130551000</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>-1096481000</v>
       </c>
     </row>
@@ -5437,10 +5824,16 @@
       <c r="A14" t="str">
         <v xml:space="preserve">    Finansman Kredilerindeki Net (Artış) Azalış</v>
       </c>
-      <c r="J14">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>0</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
     </row>
@@ -5448,10 +5841,16 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Alacaklarda Net (Artış) Azalış</v>
       </c>
-      <c r="J15">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
     </row>
@@ -5459,10 +5858,16 @@
       <c r="A16" t="str">
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
-      <c r="J16">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>0</v>
       </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
     </row>
@@ -5471,36 +5876,42 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-24817000</v>
+      </c>
+      <c r="C17">
         <v>5973000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>7357000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-1325000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
+        <v>-2948000</v>
+      </c>
+      <c r="G17">
         <v>89016000</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>104274000</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>48497000</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-12339000</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-235129000</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-138698000</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>12202000</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>-58717000</v>
       </c>
     </row>
@@ -5509,36 +5920,42 @@
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
       <c r="B18">
+        <v>2120000</v>
+      </c>
+      <c r="C18">
         <v>-365000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>5589000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>-366000</v>
       </c>
-      <c r="E18">
+      <c r="F18">
+        <v>9873000</v>
+      </c>
+      <c r="G18">
         <v>286000</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>-90000</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>2052000</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>-5378000</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>-3513000</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>-1841000</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>-6824000</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>6637000</v>
       </c>
     </row>
@@ -5546,10 +5963,16 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
-      <c r="J19">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>0</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>0</v>
       </c>
     </row>
@@ -5558,36 +5981,42 @@
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B20">
+        <v>-3169000</v>
+      </c>
+      <c r="C20">
         <v>-7712000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-4552000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-2881000</v>
       </c>
-      <c r="E20">
+      <c r="F20">
+        <v>-334000</v>
+      </c>
+      <c r="G20">
         <v>11497000</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>11662000</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>10746000</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>5607000</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-351000</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>-1471000</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>-802000</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>242000</v>
       </c>
     </row>
@@ -5596,36 +6025,42 @@
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
       <c r="B21">
+        <v>-6755274000</v>
+      </c>
+      <c r="C21">
         <v>6052733000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>-4331381000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>-1946339000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
+        <v>-11696944000</v>
+      </c>
+      <c r="G21">
         <v>-6699356000</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>-12088837000</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>-556218000</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>11909592000</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>2945411000</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>14632789000</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>2554514000</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>899872000</v>
       </c>
     </row>
@@ -5633,10 +6068,16 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Vadesi Gelmiş Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="J22">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>0</v>
       </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="N22">
         <v>0</v>
       </c>
     </row>
@@ -5645,36 +6086,42 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>29945000</v>
+      </c>
+      <c r="C23">
         <v>11578000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-8046000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-29467000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
+        <v>54537000</v>
+      </c>
+      <c r="G23">
         <v>-18728000</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>17524000</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>-24928000</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>18068000</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>588817000</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>62089000</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>-52464000</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>75507000</v>
       </c>
     </row>
@@ -5683,36 +6130,42 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>181242000</v>
+      </c>
+      <c r="C24">
         <v>-958742000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-532936000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-561966000</v>
       </c>
-      <c r="E24">
+      <c r="F24">
+        <v>192277000</v>
+      </c>
+      <c r="G24">
         <v>-305182000</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>400905000</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>351035000</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>-300674000</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>1767254000</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>-609162000</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>263330000</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>14070000</v>
       </c>
     </row>
@@ -5720,10 +6173,16 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
-      <c r="J25">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>0</v>
       </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
     </row>
@@ -5737,36 +6196,42 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-1420000</v>
+      </c>
+      <c r="C27">
         <v>-3991000</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-3347000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>-2115000</v>
       </c>
-      <c r="E27">
+      <c r="F27">
+        <v>-2015000</v>
+      </c>
+      <c r="G27">
         <v>-5419000</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>-16666000</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>-13867000</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>-8079000</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>-304000</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>-4121000</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>-491000</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>-1894000</v>
       </c>
     </row>
@@ -5775,27 +6240,33 @@
         <v xml:space="preserve">    Elden Çıkarılan Menkul ve Gayrimenkuller</v>
       </c>
       <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>239000</v>
-      </c>
-      <c r="C28">
-        <v>230000</v>
       </c>
       <c r="D28">
         <v>230000</v>
       </c>
-      <c r="H28">
+      <c r="E28">
+        <v>230000</v>
+      </c>
+      <c r="F28">
+        <v>230000</v>
+      </c>
+      <c r="J28">
         <v>826000</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>91000</v>
       </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>81000</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>120000</v>
       </c>
     </row>
@@ -5803,10 +6274,16 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Elde Edilen Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıklar</v>
       </c>
-      <c r="J29">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="N29">
         <v>0</v>
       </c>
     </row>
@@ -5819,10 +6296,16 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Satın Alınan İtfa Edilmiş Maliyeti ile Ölçülen Finansal Varlıklar</v>
       </c>
-      <c r="J31">
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <v>0</v>
       </c>
       <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="N31">
         <v>0</v>
       </c>
     </row>
@@ -5835,10 +6318,16 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="J33">
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>0</v>
       </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="N33">
         <v>-1736000</v>
       </c>
     </row>
@@ -5847,36 +6336,42 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-1420000</v>
+      </c>
+      <c r="C34">
         <v>53051000</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>16883000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>-1885000</v>
       </c>
-      <c r="E34">
+      <c r="F34">
+        <v>-1785000</v>
+      </c>
+      <c r="G34">
         <v>-5419000</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>-16666000</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>-13867000</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>-7253000</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>-213000</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>-4121000</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>-410000</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>-3510000</v>
       </c>
     </row>
@@ -5890,33 +6385,39 @@
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
       <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>-640415000</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-237548000</v>
       </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
       <c r="F36">
+        <v>-289990000</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>-105628000</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>-105628000</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-1513520000</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-618627000</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-767915000</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <v>581475000</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>-1957932000</v>
       </c>
     </row>
@@ -5929,10 +6430,13 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
-      <c r="J38">
+      <c r="B38">
         <v>0</v>
       </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="N38">
         <v>0</v>
       </c>
     </row>
@@ -5940,10 +6444,13 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
-      <c r="J39">
+      <c r="B39">
         <v>0</v>
       </c>
       <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="N39">
         <v>-1766000</v>
       </c>
     </row>
@@ -5951,10 +6458,10 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="N40">
         <v>0</v>
       </c>
     </row>
@@ -5963,36 +6470,42 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>-93917000</v>
+      </c>
+      <c r="C41">
         <v>693010000</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>402867000</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>640415000</v>
       </c>
-      <c r="E41">
+      <c r="F41">
+        <v>-289990000</v>
+      </c>
+      <c r="G41">
         <v>105628000</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>-105628000</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>-105628000</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>611665000</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>-163639000</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>684285000</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>-186440000</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>-8560000</v>
       </c>
     </row>
@@ -6001,36 +6514,42 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
       <c r="B42">
+        <v>1030000</v>
+      </c>
+      <c r="C42">
         <v>3697000</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>3910000</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>1093000</v>
       </c>
-      <c r="E42">
+      <c r="F42">
+        <v>1754000</v>
+      </c>
+      <c r="G42">
         <v>2433000</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>2751000</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>1768000</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>30371000</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>11201000</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>8608000</v>
       </c>
-      <c r="K42">
+      <c r="M42">
         <v>23655000</v>
       </c>
-      <c r="L42">
+      <c r="N42">
         <v>14140000</v>
       </c>
     </row>
@@ -6039,36 +6558,42 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>86935000</v>
+      </c>
+      <c r="C43">
         <v>-208984000</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-109276000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>77657000</v>
       </c>
-      <c r="E43">
+      <c r="F43">
+        <v>-97744000</v>
+      </c>
+      <c r="G43">
         <v>-202540000</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>281362000</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>233308000</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>334109000</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>1614603000</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>79610000</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>100135000</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>16140000</v>
       </c>
     </row>
@@ -6084,14 +6609,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:N45"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6105,6 +6630,8 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6112,36 +6639,42 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -6155,15 +6688,24 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>-179034000</v>
+      </c>
+      <c r="C3">
         <v>1559175000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>130973000</v>
       </c>
       <c r="E3">
+        <v>941713000</v>
+      </c>
+      <c r="F3">
+        <v>-451646000</v>
+      </c>
+      <c r="G3">
         <v>-348176000</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>-740083000</v>
       </c>
     </row>
@@ -6172,15 +6714,24 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>1637061000</v>
+      </c>
+      <c r="C4">
         <v>2801698000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2141862000</v>
       </c>
       <c r="E4">
+        <v>2669548000</v>
+      </c>
+      <c r="F4">
+        <v>1952588000</v>
+      </c>
+      <c r="G4">
         <v>2817744000</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>3341672000</v>
       </c>
     </row>
@@ -6189,15 +6740,24 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-1525646000</v>
+      </c>
+      <c r="C5">
         <v>-935851000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-1729835000</v>
       </c>
       <c r="E5">
+        <v>-1264173000</v>
+      </c>
+      <c r="F5">
+        <v>-2352937000</v>
+      </c>
+      <c r="G5">
         <v>-2942080000</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>-3803067000</v>
       </c>
     </row>
@@ -6205,21 +6765,36 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>2164000</v>
+      </c>
+      <c r="C7">
         <v>1913000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>2842000</v>
       </c>
       <c r="E7">
+        <v>3529000</v>
+      </c>
+      <c r="F7">
+        <v>2545000</v>
+      </c>
+      <c r="G7">
         <v>3838000</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>6703000</v>
       </c>
     </row>
@@ -6228,15 +6803,24 @@
         <v xml:space="preserve">    Zarar Olarak Muhasebeleştirilen Takipteki Alacaklardan Tahsilatlar</v>
       </c>
       <c r="B8">
+        <v>84000</v>
+      </c>
+      <c r="C8">
         <v>95000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>136000</v>
       </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>213000</v>
+      </c>
+      <c r="G8">
         <v>316000</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>483000</v>
       </c>
     </row>
@@ -6245,15 +6829,24 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-60360000</v>
+      </c>
+      <c r="C9">
         <v>-49834000</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-49136000</v>
       </c>
       <c r="E9">
+        <v>-53085000</v>
+      </c>
+      <c r="F9">
+        <v>-43874000</v>
+      </c>
+      <c r="G9">
         <v>-35876000</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>-35386000</v>
       </c>
     </row>
@@ -6262,15 +6855,24 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-224950000</v>
+      </c>
+      <c r="C10">
         <v>-218252000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-207433000</v>
       </c>
       <c r="E10">
+        <v>-386444000</v>
+      </c>
+      <c r="F10">
+        <v>-2314000</v>
+      </c>
+      <c r="G10">
         <v>-166680000</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>-229857000</v>
       </c>
     </row>
@@ -6279,15 +6881,24 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-7387000</v>
+      </c>
+      <c r="C11">
         <v>-40594000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-27463000</v>
       </c>
       <c r="E11">
+        <v>-27662000</v>
+      </c>
+      <c r="F11">
+        <v>-7867000</v>
+      </c>
+      <c r="G11">
         <v>-25438000</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>-20631000</v>
       </c>
     </row>
@@ -6296,15 +6907,24 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>360276000</v>
+      </c>
+      <c r="C12">
         <v>-1984981000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-101943000</v>
       </c>
       <c r="E12">
+        <v>-1695956000</v>
+      </c>
+      <c r="F12">
+        <v>643923000</v>
+      </c>
+      <c r="G12">
         <v>-357911000</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>789953000</v>
       </c>
     </row>
@@ -6313,15 +6933,24 @@
         <v xml:space="preserve">    Faktoring Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B13">
+        <v>7111471000</v>
+      </c>
+      <c r="C13">
         <v>-12378221000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>2248712000</v>
       </c>
       <c r="E13">
+        <v>-11351394000</v>
+      </c>
+      <c r="F13">
+        <v>12279739000</v>
+      </c>
+      <c r="G13">
         <v>-5696093000</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>12225569000</v>
       </c>
     </row>
@@ -6329,31 +6958,58 @@
       <c r="A14" t="str">
         <v xml:space="preserve">    Finansman Kredilerindeki Net (Artış) Azalış</v>
       </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Alacaklarda Net (Artış) Azalış</v>
       </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-24817000</v>
+      </c>
+      <c r="C17">
         <v>-1384000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>8682000</v>
       </c>
       <c r="E17">
+        <v>1623000</v>
+      </c>
+      <c r="F17">
+        <v>-2948000</v>
+      </c>
+      <c r="G17">
         <v>-15258000</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>55777000</v>
       </c>
     </row>
@@ -6362,15 +7018,24 @@
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
       <c r="B18">
+        <v>2120000</v>
+      </c>
+      <c r="C18">
         <v>-5954000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>5955000</v>
       </c>
       <c r="E18">
+        <v>-10239000</v>
+      </c>
+      <c r="F18">
+        <v>9873000</v>
+      </c>
+      <c r="G18">
         <v>376000</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>-2142000</v>
       </c>
     </row>
@@ -6378,21 +7043,36 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B20">
+        <v>-3169000</v>
+      </c>
+      <c r="C20">
         <v>-3160000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-1671000</v>
       </c>
       <c r="E20">
+        <v>-2547000</v>
+      </c>
+      <c r="F20">
+        <v>-334000</v>
+      </c>
+      <c r="G20">
         <v>-165000</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>916000</v>
       </c>
     </row>
@@ -6401,15 +7081,24 @@
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
       <c r="B21">
+        <v>-6755274000</v>
+      </c>
+      <c r="C21">
         <v>10384114000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>-2385042000</v>
       </c>
       <c r="E21">
+        <v>9750605000</v>
+      </c>
+      <c r="F21">
+        <v>-11696944000</v>
+      </c>
+      <c r="G21">
         <v>5389481000</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>-11532619000</v>
       </c>
     </row>
@@ -6417,21 +7106,36 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Vadesi Gelmiş Borçlarda Net Artış (Azalış)</v>
       </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>29945000</v>
+      </c>
+      <c r="C23">
         <v>19624000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>21421000</v>
       </c>
       <c r="E23">
+        <v>-84004000</v>
+      </c>
+      <c r="F23">
+        <v>54537000</v>
+      </c>
+      <c r="G23">
         <v>-36252000</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>42452000</v>
       </c>
     </row>
@@ -6440,15 +7144,24 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>181242000</v>
+      </c>
+      <c r="C24">
         <v>-425806000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>29030000</v>
       </c>
       <c r="E24">
+        <v>-754243000</v>
+      </c>
+      <c r="F24">
+        <v>192277000</v>
+      </c>
+      <c r="G24">
         <v>-706087000</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>49870000</v>
       </c>
     </row>
@@ -6456,6 +7169,12 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -6467,15 +7186,24 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-1420000</v>
+      </c>
+      <c r="C27">
         <v>-644000</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-1232000</v>
       </c>
       <c r="E27">
+        <v>-100000</v>
+      </c>
+      <c r="F27">
+        <v>-2015000</v>
+      </c>
+      <c r="G27">
         <v>11247000</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>-2799000</v>
       </c>
     </row>
@@ -6484,16 +7212,31 @@
         <v xml:space="preserve">    Elden Çıkarılan Menkul ve Gayrimenkuller</v>
       </c>
       <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>9000</v>
       </c>
-      <c r="C28">
-        <v>0</v>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>230000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Elde Edilen Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıklar</v>
       </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -6504,6 +7247,12 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Satın Alınan İtfa Edilmiş Maliyeti ile Ölçülen Finansal Varlıklar</v>
       </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -6514,21 +7263,36 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-1420000</v>
+      </c>
+      <c r="C34">
         <v>36168000</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>18768000</v>
       </c>
       <c r="E34">
+        <v>-100000</v>
+      </c>
+      <c r="F34">
+        <v>-1785000</v>
+      </c>
+      <c r="G34">
         <v>11247000</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>-2799000</v>
       </c>
     </row>
@@ -6542,12 +7306,18 @@
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
       <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>-402867000</v>
       </c>
-      <c r="E36">
+      <c r="F36">
+        <v>-289990000</v>
+      </c>
+      <c r="G36">
         <v>105628000</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>0</v>
       </c>
     </row>
@@ -6560,11 +7330,17 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -6576,15 +7352,24 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>-93917000</v>
+      </c>
+      <c r="C41">
         <v>290143000</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>-237548000</v>
       </c>
       <c r="E41">
+        <v>930405000</v>
+      </c>
+      <c r="F41">
+        <v>-289990000</v>
+      </c>
+      <c r="G41">
         <v>211256000</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>0</v>
       </c>
     </row>
@@ -6593,15 +7378,24 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
       <c r="B42">
+        <v>1030000</v>
+      </c>
+      <c r="C42">
         <v>-213000</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>2817000</v>
       </c>
       <c r="E42">
+        <v>-661000</v>
+      </c>
+      <c r="F42">
+        <v>1754000</v>
+      </c>
+      <c r="G42">
         <v>-318000</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>983000</v>
       </c>
     </row>
@@ -6610,15 +7404,24 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>86935000</v>
+      </c>
+      <c r="C43">
         <v>-99708000</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-186933000</v>
       </c>
       <c r="E43">
+        <v>175401000</v>
+      </c>
+      <c r="F43">
+        <v>-97744000</v>
+      </c>
+      <c r="G43">
         <v>-483902000</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>48054000</v>
       </c>
     </row>
@@ -6634,14 +7437,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:N45"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6655,6 +7458,8 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6662,36 +7467,42 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -6705,30 +7516,33 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>2452827000</v>
+      </c>
+      <c r="C3">
         <v>2180215000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>272864000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>-598192000</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>1115003000</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>3138896000</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>1881309000</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>1321653000</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>263233000</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>187010000</v>
       </c>
     </row>
@@ -6737,30 +7551,33 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>9250169000</v>
+      </c>
+      <c r="C4">
         <v>9565696000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9581742000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>10781552000</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>12952560000</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>10880283000</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>6814870000</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>4235833000</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>2226469000</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>570734000</v>
       </c>
     </row>
@@ -6769,30 +7586,33 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-5455505000</v>
+      </c>
+      <c r="C5">
         <v>-6282796000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-8289025000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>-10362257000</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>-10948614000</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>-7683973000</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>-5474956000</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>-3019892000</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>-1588750000</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>-515777000</v>
       </c>
     </row>
@@ -6800,10 +7620,10 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
     </row>
@@ -6812,30 +7632,33 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>10448000</v>
+      </c>
+      <c r="C7">
         <v>10829000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>12754000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>16615000</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>21825000</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>765048000</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>1164455000</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>428432000</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>21394000</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>2811000</v>
       </c>
     </row>
@@ -6844,30 +7667,33 @@
         <v xml:space="preserve">    Zarar Olarak Muhasebeleştirilen Takipteki Alacaklardan Tahsilatlar</v>
       </c>
       <c r="B8">
+        <v>315000</v>
+      </c>
+      <c r="C8">
         <v>444000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>665000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1012000</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>1264000</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>-6797000</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>-5619000</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>-9621000</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>-7088000</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>6641000</v>
       </c>
     </row>
@@ -6876,30 +7702,33 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-212415000</v>
+      </c>
+      <c r="C9">
         <v>-195929000</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-181971000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>-168221000</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>-137475000</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>-107266000</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>-68722000</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>-42299000</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>-31141000</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-31036000</v>
       </c>
     </row>
@@ -6908,30 +7737,33 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-1037079000</v>
+      </c>
+      <c r="C10">
         <v>-814443000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-762871000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-785295000</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-722637000</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>-705857000</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-539203000</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-212616000</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>-116124000</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-33110000</v>
       </c>
     </row>
@@ -6940,30 +7772,33 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-103106000</v>
+      </c>
+      <c r="C11">
         <v>-103586000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-88430000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>-81598000</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>-51920000</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>-2542000</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>-9516000</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>-58184000</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>-241527000</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>179882000</v>
       </c>
     </row>
@@ -6972,30 +7807,33 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>-3422604000</v>
+      </c>
+      <c r="C12">
         <v>-3138957000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-1511887000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-619991000</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>-1420185000</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-4855789000</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-2181983000</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-426891000</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>-872395000</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>-172940000</v>
       </c>
     </row>
@@ -7004,30 +7842,33 @@
         <v xml:space="preserve">    Faktoring Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B13">
+        <v>-14369432000</v>
+      </c>
+      <c r="C13">
         <v>-9201164000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>-2519036000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>7457821000</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>5197100000</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>-12956253000</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>-14097533000</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>-15768368000</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>-15425263000</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>-1096481000</v>
       </c>
     </row>
@@ -7035,10 +7876,10 @@
       <c r="A14" t="str">
         <v xml:space="preserve">    Finansman Kredilerindeki Net (Artış) Azalış</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
     </row>
@@ -7046,10 +7887,10 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Alacaklarda Net (Artış) Azalış</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
     </row>
@@ -7057,10 +7898,10 @@
       <c r="A16" t="str">
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
     </row>
@@ -7069,30 +7910,33 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-15896000</v>
+      </c>
+      <c r="C17">
         <v>5973000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-7901000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>39194000</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>89016000</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>271287000</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-12339000</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-386029000</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-138698000</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>-58717000</v>
       </c>
     </row>
@@ -7101,30 +7945,33 @@
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
       <c r="B18">
+        <v>-8118000</v>
+      </c>
+      <c r="C18">
         <v>-365000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>5965000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>-2132000</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>286000</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>187000</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>-5378000</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>1470000</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>-1841000</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>6637000</v>
       </c>
     </row>
@@ -7132,10 +7979,10 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>0</v>
       </c>
     </row>
@@ -7144,30 +7991,33 @@
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B20">
+        <v>-10547000</v>
+      </c>
+      <c r="C20">
         <v>-7712000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-4717000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-2130000</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>11497000</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>16704000</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>5607000</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-1020000</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>-1471000</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>242000</v>
       </c>
     </row>
@@ -7176,30 +8026,33 @@
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
       <c r="B21">
+        <v>10994403000</v>
+      </c>
+      <c r="C21">
         <v>6052733000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>1058100000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>-8089477000</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>-6699356000</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>8407963000</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>11909592000</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>15023686000</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>14632789000</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>899872000</v>
       </c>
     </row>
@@ -7207,10 +8060,10 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Vadesi Gelmiş Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="N22">
         <v>0</v>
       </c>
     </row>
@@ -7219,30 +8072,33 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>-13014000</v>
+      </c>
+      <c r="C23">
         <v>11578000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-44298000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-23267000</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>-18728000</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>-595677000</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>18068000</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>703370000</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>62089000</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>75507000</v>
       </c>
     </row>
@@ -7251,30 +8107,33 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>-969777000</v>
+      </c>
+      <c r="C24">
         <v>-958742000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-1239023000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-1218183000</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>-305182000</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>-1716893000</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>-300674000</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>894762000</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>-609162000</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>14070000</v>
       </c>
     </row>
@@ -7282,10 +8141,10 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
     </row>
@@ -7299,30 +8158,33 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-3396000</v>
+      </c>
+      <c r="C27">
         <v>-3991000</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>7900000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>6333000</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>-5419000</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>-21642000</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>-8079000</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>-3934000</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>-4121000</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>-1894000</v>
       </c>
     </row>
@@ -7331,18 +8193,21 @@
         <v xml:space="preserve">    Elden Çıkarılan Menkul ve Gayrimenkuller</v>
       </c>
       <c r="B28">
+        <v>9000</v>
+      </c>
+      <c r="C28">
         <v>239000</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>826000</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>10000</v>
       </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
       <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="N28">
         <v>120000</v>
       </c>
     </row>
@@ -7350,10 +8215,10 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Elde Edilen Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıklar</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="N29">
         <v>0</v>
       </c>
     </row>
@@ -7366,10 +8231,10 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Satın Alınan İtfa Edilmiş Maliyeti ile Ölçülen Finansal Varlıklar</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
       <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="N31">
         <v>0</v>
       </c>
     </row>
@@ -7382,10 +8247,10 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="N33">
         <v>-1736000</v>
       </c>
     </row>
@@ -7394,30 +8259,33 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>53416000</v>
+      </c>
+      <c r="C34">
         <v>53051000</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>28130000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>6563000</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>-5419000</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>-20907000</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>-7253000</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>-3924000</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>-4121000</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>-3510000</v>
       </c>
     </row>
@@ -7431,27 +8299,30 @@
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
       <c r="B36">
+        <v>-350425000</v>
+      </c>
+      <c r="C36">
         <v>-640415000</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-131920000</v>
       </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="I36">
         <v>-1000521000</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-1513520000</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-1968017000</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-767915000</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>-1957932000</v>
       </c>
     </row>
@@ -7464,10 +8335,10 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="N38">
         <v>0</v>
       </c>
     </row>
@@ -7475,10 +8346,10 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
       <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="N39">
         <v>-1766000</v>
       </c>
     </row>
@@ -7486,10 +8357,10 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="N40">
         <v>0</v>
       </c>
     </row>
@@ -7498,30 +8369,33 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>889083000</v>
+      </c>
+      <c r="C41">
         <v>693010000</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>614123000</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>851671000</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>105628000</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>669676000</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>611665000</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>707086000</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>684285000</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>-8560000</v>
       </c>
     </row>
@@ -7530,30 +8404,33 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
       <c r="B42">
+        <v>2973000</v>
+      </c>
+      <c r="C42">
         <v>3697000</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>3592000</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>1758000</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>2433000</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>20938000</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>30371000</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>-3846000</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>8608000</v>
       </c>
-      <c r="L42">
+      <c r="N42">
         <v>14140000</v>
       </c>
     </row>
@@ -7562,30 +8439,33 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>-24305000</v>
+      </c>
+      <c r="C43">
         <v>-208984000</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-593178000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>-358191000</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>-202540000</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>-1047186000</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>334109000</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>1594078000</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>79610000</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>16140000</v>
       </c>
     </row>
@@ -7601,7 +8481,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/VAKFA (TRY).xlsx
+++ b/data/VAKFA (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -416,6 +416,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,33 +424,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -463,33 +467,36 @@
         <v xml:space="preserve">    Nakit, Nakit Benzerleri ve Merkez Bankası</v>
       </c>
       <c r="B3">
+        <v>630145000</v>
+      </c>
+      <c r="C3">
         <v>184568000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>97569000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>197394000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>384598000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>306833000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>745298000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>510523000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1794960000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>174993000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>95321000</v>
       </c>
     </row>
@@ -498,33 +505,36 @@
         <v xml:space="preserve">    İtfa Edilmiş Maliyet ile Ölçülen Finansal Varlıklar (Net)</v>
       </c>
       <c r="B4">
+        <v>45991931000</v>
+      </c>
+      <c r="C4">
         <v>34796434000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>41713384000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>29833081000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>31839448000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>32424129000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>39078584000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>37481289000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>25025122000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>22611298000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>7008665000</v>
       </c>
     </row>
@@ -532,16 +542,16 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Tasarruf Finansman Alacakları</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>0</v>
       </c>
     </row>
@@ -550,33 +560,36 @@
         <v xml:space="preserve">    Faktoring Alacakları</v>
       </c>
       <c r="B6">
+        <v>45991931000</v>
+      </c>
+      <c r="C6">
         <v>34796434000</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>41713384000</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>29833081000</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>31839448000</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>32424129000</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>39078584000</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>37455124000</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>24983259000</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>22611298000</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>7006937000</v>
       </c>
     </row>
@@ -585,33 +598,36 @@
         <v xml:space="preserve">    Takipteki Alacaklar</v>
       </c>
       <c r="B7">
+        <v>96874000</v>
+      </c>
+      <c r="C7">
         <v>97282000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>97366000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>97461000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>97579000</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>97810000</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>98609000</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>99074000</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>103050000</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>52363000</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>66879000</v>
       </c>
     </row>
@@ -620,33 +636,36 @@
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları / Özel Karşılıklar (-)</v>
       </c>
       <c r="B8">
+        <v>-96874000</v>
+      </c>
+      <c r="C8">
         <v>-97282000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-97366000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>-97461000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>-97579000</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>-97810000</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>-98609000</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>-72909000</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>-61187000</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>-52363000</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>-65151000</v>
       </c>
     </row>
@@ -684,39 +703,45 @@
       <c r="K9">
         <v>0</v>
       </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Maddi Duran Varlıklar (Net)</v>
       </c>
       <c r="B10">
+        <v>9569000</v>
+      </c>
+      <c r="C10">
         <v>7573000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>10336000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>13518000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>15444000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>19308000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>18369000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>8278000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>3053000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>4027000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>2558000</v>
       </c>
     </row>
@@ -725,33 +750,36 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar (Net)</v>
       </c>
       <c r="B11">
+        <v>2266000</v>
+      </c>
+      <c r="C11">
         <v>1978000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>1091000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>705000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>867000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>1053000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>847000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>997000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1496000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1856000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>2069000</v>
       </c>
     </row>
@@ -789,6 +817,9 @@
       <c r="K12">
         <v>0</v>
       </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -810,18 +841,21 @@
         <v>0</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>7524000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1487000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>1028000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>203000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>158000</v>
       </c>
     </row>
@@ -830,33 +864,36 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B14">
+        <v>44027000</v>
+      </c>
+      <c r="C14">
         <v>37140000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>29561000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>21236000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>21275000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>20506000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>4160000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>946000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>547000</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>51219000</v>
       </c>
     </row>
@@ -865,33 +902,36 @@
         <v xml:space="preserve">    Diğer Aktifler</v>
       </c>
       <c r="B15">
+        <v>54503000</v>
+      </c>
+      <c r="C15">
         <v>42198000</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>37046000</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>80528000</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>59020000</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>67043000</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>125285000</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>190464000</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>411474000</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>182856000</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>11080000</v>
       </c>
     </row>
@@ -900,33 +940,36 @@
         <v xml:space="preserve">    (ARA TOPLAM) 1</v>
       </c>
       <c r="B16">
+        <v>46732441000</v>
+      </c>
+      <c r="C16">
         <v>35069891000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>41888987000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>30146462000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>32377455000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>32888590000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>40021854000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>38235771000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>27263871000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>23001424000</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>7179227000</v>
       </c>
     </row>
@@ -964,39 +1007,45 @@
       <c r="K17">
         <v>220000</v>
       </c>
+      <c r="L17">
+        <v>220000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v xml:space="preserve">    TOPLAM VARLIKLAR</v>
       </c>
       <c r="B18">
+        <v>46732661000</v>
+      </c>
+      <c r="C18">
         <v>35070111000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>41889207000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>30146682000</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>32377675000</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>32888810000</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>40022074000</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>38235991000</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>27264091000</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>23001644000</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>7179447000</v>
       </c>
     </row>
@@ -1005,33 +1054,36 @@
         <v xml:space="preserve">    YÜKÜMLÜLÜKLER TOPLAMI</v>
       </c>
       <c r="B19">
+        <v>38808871000</v>
+      </c>
+      <c r="C19">
         <v>27693479000</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>34880244000</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>24340834000</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>27098201000</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>28497715000</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>36470647000</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>35562528000</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>25478691000</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>21847344000</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>6588773000</v>
       </c>
     </row>
@@ -1040,33 +1092,36 @@
         <v xml:space="preserve">    Alınan Krediler</v>
       </c>
       <c r="B20">
+        <v>38341003000</v>
+      </c>
+      <c r="C20">
         <v>27301272000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>34499576000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>23578599000</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>26142311000</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>28141846000</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>36099092000</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>33000633000</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>23406668000</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>20158989000</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>5483580000</v>
       </c>
     </row>
@@ -1075,33 +1130,36 @@
         <v xml:space="preserve">    Faktoring Borçları</v>
       </c>
       <c r="B21">
+        <v>12965000</v>
+      </c>
+      <c r="C21">
         <v>2131000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>11000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>5965000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>10000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>376000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2142000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>90000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>1955000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>5468000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>7309000</v>
       </c>
     </row>
@@ -1139,39 +1197,45 @@
       <c r="K22">
         <v>0</v>
       </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlar</v>
       </c>
       <c r="B23">
+        <v>8889000</v>
+      </c>
+      <c r="C23">
         <v>7113000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>10282000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>13442000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>15113000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>17994000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>17243000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>6497000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>539000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>890000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>2361000</v>
       </c>
     </row>
@@ -1186,27 +1250,30 @@
         <v>0</v>
       </c>
       <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
         <v>402867000</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>640415000</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>2228522000</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1310605000</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>1513520000</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>767915000</v>
       </c>
     </row>
@@ -1215,33 +1282,36 @@
         <v xml:space="preserve">    Karşılıklar</v>
       </c>
       <c r="B25">
+        <v>147693000</v>
+      </c>
+      <c r="C25">
         <v>124151000</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>98350000</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>69966000</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>70226000</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>68285000</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>82865000</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>73500000</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>61343000</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>46847000</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>33424000</v>
       </c>
     </row>
@@ -1250,33 +1320,36 @@
         <v xml:space="preserve">    Cari Vergi Borcu</v>
       </c>
       <c r="B26">
+        <v>288533000</v>
+      </c>
+      <c r="C26">
         <v>246783000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>253665000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>257332000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>225673000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>258406000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>265917000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>231124000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>155346000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>96482000</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>70271000</v>
       </c>
     </row>
@@ -1309,9 +1382,12 @@
         <v>0</v>
       </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>137000</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>0</v>
       </c>
     </row>
@@ -1320,33 +1396,36 @@
         <v xml:space="preserve">    Diğer Yükümlülükler</v>
       </c>
       <c r="B28">
+        <v>9788000</v>
+      </c>
+      <c r="C28">
         <v>12029000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>18360000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>12663000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>4453000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>10808000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>3388000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>22162000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>542235000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>25011000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>2851000</v>
       </c>
     </row>
@@ -1355,33 +1434,36 @@
         <v xml:space="preserve">    (ARA TOPLAM) 2</v>
       </c>
       <c r="B29">
+        <v>38808871000</v>
+      </c>
+      <c r="C29">
         <v>27693479000</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>34880244000</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>24340834000</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>27098201000</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>28497715000</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>36470647000</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>35562528000</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>25478691000</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>21847344000</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>6588773000</v>
       </c>
     </row>
@@ -1419,39 +1501,45 @@
       <c r="K30">
         <v>0</v>
       </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v xml:space="preserve">    ÖZKAYNAKLAR</v>
       </c>
       <c r="B31">
+        <v>7923790000</v>
+      </c>
+      <c r="C31">
         <v>7376632000</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>7008963000</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>5805848000</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>5279474000</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>4391095000</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>3551427000</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>2673463000</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>1785400000</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>1154300000</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>590674000</v>
       </c>
     </row>
@@ -1466,7 +1554,7 @@
         <v>900000000</v>
       </c>
       <c r="D32">
-        <v>850000000</v>
+        <v>900000000</v>
       </c>
       <c r="E32">
         <v>850000000</v>
@@ -1481,12 +1569,15 @@
         <v>850000000</v>
       </c>
       <c r="I32">
-        <v>450000000</v>
+        <v>850000000</v>
       </c>
       <c r="J32">
         <v>450000000</v>
       </c>
       <c r="K32">
+        <v>450000000</v>
+      </c>
+      <c r="L32">
         <v>350000000</v>
       </c>
     </row>
@@ -1504,24 +1595,27 @@
         <v>51000</v>
       </c>
       <c r="E33">
+        <v>51000</v>
+      </c>
+      <c r="F33">
         <v>54466000</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>47381000</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>39450000</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>36928000</v>
-      </c>
-      <c r="I33">
-        <v>22501000</v>
       </c>
       <c r="J33">
         <v>22501000</v>
       </c>
       <c r="K33">
+        <v>22501000</v>
+      </c>
+      <c r="L33">
         <v>5595000</v>
       </c>
     </row>
@@ -1530,7 +1624,7 @@
         <v xml:space="preserve">    Kar Yedekleri</v>
       </c>
       <c r="B34">
-        <v>3496807000</v>
+        <v>5465902000</v>
       </c>
       <c r="C34">
         <v>3496807000</v>
@@ -1539,24 +1633,27 @@
         <v>3496807000</v>
       </c>
       <c r="E34">
+        <v>3496807000</v>
+      </c>
+      <c r="F34">
         <v>3493714000</v>
-      </c>
-      <c r="F34">
-        <v>1786535000</v>
       </c>
       <c r="G34">
         <v>1786535000</v>
       </c>
       <c r="H34">
+        <v>1786535000</v>
+      </c>
+      <c r="I34">
         <v>281799000</v>
-      </c>
-      <c r="I34">
-        <v>135079000</v>
       </c>
       <c r="J34">
         <v>135079000</v>
       </c>
       <c r="K34">
+        <v>135079000</v>
+      </c>
+      <c r="L34">
         <v>118793000</v>
       </c>
     </row>
@@ -1565,27 +1662,30 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar veya Zararı</v>
       </c>
       <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>1969095000</v>
-      </c>
-      <c r="C35">
-        <v>44237000</v>
       </c>
       <c r="D35">
         <v>44237000</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="H35">
+      <c r="E35">
+        <v>44237000</v>
+      </c>
+      <c r="G35">
         <v>0</v>
       </c>
       <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
         <v>546720000</v>
       </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
       <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>0</v>
       </c>
     </row>
@@ -1594,33 +1694,36 @@
         <v xml:space="preserve">    Dönem Net Karı veya Zararı</v>
       </c>
       <c r="B36">
+        <v>1008743000</v>
+      </c>
+      <c r="C36">
         <v>461585000</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>1924858000</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>1414753000</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>881294000</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>1707179000</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>875442000</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>1504736000</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>631100000</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>546720000</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>116286000</v>
       </c>
     </row>
@@ -1628,10 +1731,10 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Kontrol Gücü Olmayan Paylar</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="F37">
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>0</v>
       </c>
     </row>
@@ -1640,33 +1743,36 @@
         <v xml:space="preserve">    TOPLAM KAYNAKLAR</v>
       </c>
       <c r="B38">
+        <v>46732661000</v>
+      </c>
+      <c r="C38">
         <v>35070111000</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>41889207000</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>30146682000</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>32377675000</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>32888810000</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>40022074000</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>38235991000</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>27264091000</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>23001644000</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>7179447000</v>
       </c>
     </row>
@@ -1674,17 +1780,23 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B39">
+        <v>2339000</v>
+      </c>
+      <c r="C39">
+        <v>8103000</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:R30"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1703,6 +1815,7 @@
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
     <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1710,51 +1823,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2022/3</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -1768,51 +1884,54 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>3856045000</v>
+      </c>
+      <c r="C3">
         <v>1852213000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>9574437000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>7255446000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>4926193000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2653970000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>12809590000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>10280627000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>6918423000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>3225693000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>8670672000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>3095297000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1319228000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>2429221000</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>725811000</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>315929000</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>772176000</v>
       </c>
     </row>
@@ -1821,51 +1940,54 @@
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
       <c r="B4">
+        <v>3856045000</v>
+      </c>
+      <c r="C4">
         <v>1852213000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9574437000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>7255446000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>4926193000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>2653970000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>12809590000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>10280627000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>6918423000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>3225693000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>8670672000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>3095297000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1319228000</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2429221000</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>725811000</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>315929000</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>772176000</v>
       </c>
     </row>
@@ -1895,6 +2017,9 @@
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1926,6 +2051,9 @@
         <v>0</v>
       </c>
       <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>0</v>
       </c>
     </row>
@@ -1945,6 +2073,9 @@
       <c r="E8">
         <v>0</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1976,6 +2107,9 @@
         <v>0</v>
       </c>
       <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>0</v>
       </c>
     </row>
@@ -2031,57 +2165,63 @@
       <c r="Q9">
         <v>0</v>
       </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-2180672000</v>
+      </c>
+      <c r="C10">
         <v>-1082616000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-6587793000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-5115079000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-3563914000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-2006492000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-10455033000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-8594106000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-5735250000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-2770469000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-6510345000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-2257442000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>-977003000</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>-1692690000</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>-532733000</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>-238125000</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>-603973000</v>
       </c>
     </row>
@@ -2090,51 +2230,54 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>1675373000</v>
+      </c>
+      <c r="C11">
         <v>769597000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>2986644000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>2140367000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>1362279000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>647478000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>2354557000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1686521000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1183173000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>455224000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>2160327000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>837855000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>342225000</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>736531000</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>193078000</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>77804000</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>168203000</v>
       </c>
     </row>
@@ -2143,51 +2286,54 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-210966000</v>
+      </c>
+      <c r="C12">
         <v>-91735000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-336575000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-229534000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-145518000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>-60347000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-230783000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-147628000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-89465000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-41351000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-133733000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-45145000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>-18901000</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>-59165000</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>-20493000</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>-9029000</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>-31036000</v>
       </c>
     </row>
@@ -2196,51 +2342,54 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>1464407000</v>
+      </c>
+      <c r="C13">
         <v>677862000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>2650069000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1910833000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>1216761000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>587131000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>2123774000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1538893000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>1093708000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>413873000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>2026594000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>792710000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>323324000</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>677366000</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>172585000</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>68775000</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>137167000</v>
       </c>
     </row>
@@ -2249,51 +2398,54 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>1841857000</v>
+      </c>
+      <c r="C14">
         <v>977354000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>3497681000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>2925765000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>2298926000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1014111000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1945553000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1413539000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>762742000</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>532667000</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1857587000</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1038385000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>172696000</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>1286478000</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>917044000</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>575666000</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>1141711000</v>
       </c>
     </row>
@@ -2302,14 +2454,14 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-43950000</v>
+      </c>
+      <c r="C15">
         <v>-23950000</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-26650000</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
@@ -2317,36 +2469,39 @@
         <v>0</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>-79615000</v>
-      </c>
-      <c r="H15">
-        <v>-26165000</v>
       </c>
       <c r="I15">
         <v>-26165000</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>-26165000</v>
       </c>
       <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>-26165000</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>-10467000</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>-7440000</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>-1972000</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>-71000</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>-8861000</v>
       </c>
     </row>
@@ -2355,51 +2510,54 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-1820606000</v>
+      </c>
+      <c r="C16">
         <v>-971517000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-3372971000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-2817557000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-2256025000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-996619000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-1549037000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-1132981000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-578747000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-457826000</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-1709507000</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-980135000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>-145818000</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>-1233939000</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>-877718000</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>-540279000</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>-1109218000</v>
       </c>
     </row>
@@ -2408,51 +2566,54 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>1441708000</v>
+      </c>
+      <c r="C17">
         <v>659749000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>2748129000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>2019041000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>1259662000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>604623000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>2440675000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>1793286000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>1251538000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>488714000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>2148509000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>840493000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>350202000</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>722465000</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>209939000</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>104091000</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>160799000</v>
       </c>
     </row>
@@ -2463,22 +2624,16 @@
       <c r="B18">
         <v>0</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="I18">
         <v>0</v>
       </c>
       <c r="L18">
@@ -2497,6 +2652,9 @@
         <v>0</v>
       </c>
       <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
         <v>0</v>
       </c>
     </row>
@@ -2507,22 +2665,16 @@
       <c r="B19">
         <v>0</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="I19">
         <v>0</v>
       </c>
       <c r="L19">
@@ -2541,6 +2693,9 @@
         <v>0</v>
       </c>
       <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
         <v>0</v>
       </c>
     </row>
@@ -2551,22 +2706,16 @@
       <c r="B20">
         <v>0</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="I20">
         <v>0</v>
       </c>
       <c r="L20">
@@ -2585,6 +2734,9 @@
         <v>0</v>
       </c>
       <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
         <v>0</v>
       </c>
     </row>
@@ -2593,51 +2745,54 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>1441708000</v>
+      </c>
+      <c r="C21">
         <v>659749000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2748129000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>2019041000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>1259662000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>604623000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2440675000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1793286000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>1251538000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>488714000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>2148509000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>840493000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>350202000</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>722465000</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>209939000</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>104091000</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>160799000</v>
       </c>
     </row>
@@ -2646,51 +2801,54 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-432965000</v>
+      </c>
+      <c r="C22">
         <v>-198164000</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-823271000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-604288000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-378368000</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>-181606000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-733496000</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-538939000</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>-376096000</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>-146949000</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>-643773000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-209393000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>-86797000</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>-175745000</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>-50255000</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>-50729000</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>-44513000</v>
       </c>
     </row>
@@ -2699,51 +2857,54 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-447431000</v>
+      </c>
+      <c r="C23">
         <v>-205743000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-832326000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-605018000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-379137000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-181691000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-750535000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-539652000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-376788000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>-146931000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>-646026000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-210077000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>-87100000</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>-125516000</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
         <v>-96064000</v>
       </c>
     </row>
@@ -2781,24 +2942,27 @@
         <v>0</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>-18000</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>-50229000</v>
-      </c>
-      <c r="O25">
-        <v>-50255000</v>
       </c>
       <c r="P25">
         <v>-50255000</v>
       </c>
       <c r="Q25">
+        <v>-50255000</v>
+      </c>
+      <c r="R25">
         <v>0</v>
       </c>
     </row>
@@ -2807,51 +2971,54 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>1008743000</v>
+      </c>
+      <c r="C26">
         <v>461585000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>1924858000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1414753000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>881294000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>423017000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>1707179000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>1254347000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>875442000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>341765000</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>1504736000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>631100000</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>263405000</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>546720000</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>159684000</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>53362000</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>116286000</v>
       </c>
     </row>
@@ -2871,13 +3038,16 @@
       <c r="E27">
         <v>0</v>
       </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="I27">
         <v>0</v>
       </c>
       <c r="L27">
@@ -2896,6 +3066,9 @@
         <v>0</v>
       </c>
       <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
         <v>0</v>
       </c>
     </row>
@@ -2904,51 +3077,54 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>1008743000</v>
+      </c>
+      <c r="C28">
         <v>461585000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1924858000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>1414753000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>881294000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>423017000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>1707179000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>1254347000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>875442000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>341765000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>1504736000</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>631100000</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>263405000</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>546720000</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>159684000</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>53362000</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>116286000</v>
       </c>
     </row>
@@ -2977,7 +3153,7 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="I29">
         <v>0</v>
       </c>
       <c r="L29">
@@ -2996,6 +3172,9 @@
         <v>0</v>
       </c>
       <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
         <v>0</v>
       </c>
     </row>
@@ -3004,64 +3183,67 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>1008743000</v>
+      </c>
+      <c r="C30">
         <v>461585000</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1924858000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1414753000</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>881294000</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>423017000</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1707179000</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>1254347000</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>875442000</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>341765000</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>1504736000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>631100000</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>263405000</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>546720000</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>159684000</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>53362000</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>116286000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:R30"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3080,6 +3262,7 @@
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
     <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3087,51 +3270,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2022/3</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -3145,42 +3331,45 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>2003832000</v>
+      </c>
+      <c r="C3">
         <v>1852213000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>2318991000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2329253000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>2272223000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2653970000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>2528963000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>3362204000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3692730000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>3225693000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1776069000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1319228000</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>409882000</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>315929000</v>
       </c>
     </row>
@@ -3189,42 +3378,45 @@
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
       <c r="B4">
+        <v>2003832000</v>
+      </c>
+      <c r="C4">
         <v>1852213000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2318991000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2329253000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2272223000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>2653970000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2528963000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>3362204000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>3692730000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>3225693000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1776069000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1319228000</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>409882000</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>315929000</v>
       </c>
     </row>
@@ -3251,6 +3443,12 @@
       <c r="D7">
         <v>0</v>
       </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -3263,16 +3461,19 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7">
+      <c r="N7">
         <v>0</v>
       </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>0</v>
       </c>
     </row>
@@ -3289,6 +3490,12 @@
       <c r="D8">
         <v>0</v>
       </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -3301,16 +3508,19 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="L8">
+      <c r="K8">
         <v>0</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8">
+      <c r="N8">
         <v>0</v>
       </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>0</v>
       </c>
     </row>
@@ -3345,16 +3555,19 @@
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="L9">
+      <c r="K9">
         <v>0</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9">
+      <c r="N9">
         <v>0</v>
       </c>
       <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>0</v>
       </c>
     </row>
@@ -3363,42 +3576,45 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-1098056000</v>
+      </c>
+      <c r="C10">
         <v>-1082616000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-1472714000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-1551165000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-1557422000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-2006492000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-1860927000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-2858856000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-2964781000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-2770469000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-1280439000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>-977003000</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>-294608000</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>-238125000</v>
       </c>
     </row>
@@ -3407,42 +3623,45 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>905776000</v>
+      </c>
+      <c r="C11">
         <v>769597000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>846277000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>778088000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>714801000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>647478000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>668036000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>503348000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>727949000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>455224000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>495630000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>342225000</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>115274000</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>77804000</v>
       </c>
     </row>
@@ -3451,42 +3670,45 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-119231000</v>
+      </c>
+      <c r="C12">
         <v>-91735000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-107041000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-84016000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-85171000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>-60347000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-83155000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-58163000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-48114000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-41351000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-26244000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>-18901000</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>-11464000</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>-9029000</v>
       </c>
     </row>
@@ -3495,42 +3717,45 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>786545000</v>
+      </c>
+      <c r="C13">
         <v>677862000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>739236000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>694072000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>629630000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>587131000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>584881000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>445185000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>679835000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>413873000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>469386000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>323324000</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>103810000</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>68775000</v>
       </c>
     </row>
@@ -3539,42 +3764,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>864503000</v>
+      </c>
+      <c r="C14">
         <v>977354000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>571916000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>626839000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>1284815000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1014111000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>532014000</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>650797000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>230075000</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>532667000</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>865689000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>172696000</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>341378000</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>575666000</v>
       </c>
     </row>
@@ -3583,14 +3811,14 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-20000000</v>
+      </c>
+      <c r="C15">
         <v>-23950000</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-26650000</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
@@ -3598,27 +3826,30 @@
         <v>0</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>-53450000</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
       <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <v>-26165000</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="L15">
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>-10467000</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="O15">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>-1901000</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>-71000</v>
       </c>
     </row>
@@ -3627,42 +3858,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-849089000</v>
+      </c>
+      <c r="C16">
         <v>-971517000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-555414000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-561532000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-1259406000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-996619000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-416056000</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-554234000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-120921000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-457826000</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-834317000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>-145818000</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>-337439000</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>-540279000</v>
       </c>
     </row>
@@ -3671,42 +3905,45 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>781959000</v>
+      </c>
+      <c r="C17">
         <v>659749000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>729088000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>759379000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>655039000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>604623000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>647389000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>541748000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>762824000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>488714000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>490291000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>350202000</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>105848000</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>104091000</v>
       </c>
     </row>
@@ -3714,28 +3951,22 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="L18">
+      <c r="H18">
         <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="O18">
+      <c r="N18">
         <v>0</v>
       </c>
       <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
         <v>0</v>
       </c>
     </row>
@@ -3743,28 +3974,22 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar)</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="L19">
+      <c r="H19">
         <v>0</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="O19">
+      <c r="N19">
         <v>0</v>
       </c>
       <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <v>0</v>
       </c>
     </row>
@@ -3772,28 +3997,22 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
       <c r="D20">
         <v>0</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="L20">
+      <c r="H20">
         <v>0</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="O20">
+      <c r="N20">
         <v>0</v>
       </c>
       <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <v>0</v>
       </c>
     </row>
@@ -3802,42 +4021,45 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>781959000</v>
+      </c>
+      <c r="C21">
         <v>659749000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>729088000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>759379000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>655039000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>604623000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>647389000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>541748000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>762824000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>488714000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>490291000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>350202000</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>105848000</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>104091000</v>
       </c>
     </row>
@@ -3846,42 +4068,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-234801000</v>
+      </c>
+      <c r="C22">
         <v>-198164000</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-218983000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-225920000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-196762000</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>-181606000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-194557000</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-162843000</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>-229147000</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>-146949000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-122596000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>-86797000</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>474000</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>-50729000</v>
       </c>
     </row>
@@ -3890,42 +4115,45 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-241688000</v>
+      </c>
+      <c r="C23">
         <v>-205743000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-227308000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-225881000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-197446000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-181691000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-210883000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-162864000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-229857000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>-146931000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-122977000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>-87100000</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
       <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <v>0</v>
       </c>
     </row>
@@ -3960,21 +4188,24 @@
         <v>0</v>
       </c>
       <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>18000</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>-18000</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="O25">
+      <c r="N25">
         <v>0</v>
       </c>
       <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
         <v>-50255000</v>
       </c>
     </row>
@@ -3983,42 +4214,45 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>547158000</v>
+      </c>
+      <c r="C26">
         <v>461585000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>510105000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>533459000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>458277000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>423017000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>452832000</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>378905000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>533677000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>341765000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>367695000</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>263405000</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>106322000</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>53362000</v>
       </c>
     </row>
@@ -4035,19 +4269,28 @@
       <c r="D27">
         <v>0</v>
       </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
-      <c r="L27">
+      <c r="H27">
         <v>0</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="O27">
+      <c r="N27">
         <v>0</v>
       </c>
       <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <v>0</v>
       </c>
     </row>
@@ -4056,42 +4299,45 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>547158000</v>
+      </c>
+      <c r="C28">
         <v>461585000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>510105000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>533459000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>458277000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>423017000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>452832000</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>378905000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>533677000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>341765000</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>367695000</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>263405000</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>106322000</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>53362000</v>
       </c>
     </row>
@@ -4117,16 +4363,19 @@
       <c r="G29">
         <v>0</v>
       </c>
-      <c r="L29">
+      <c r="H29">
         <v>0</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="O29">
+      <c r="N29">
         <v>0</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>0</v>
       </c>
     </row>
@@ -4135,55 +4384,58 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>547158000</v>
+      </c>
+      <c r="C30">
         <v>461585000</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>510105000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>533459000</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>458277000</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>423017000</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>452832000</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>378905000</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>533677000</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>341765000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>367695000</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>263405000</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>106322000</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>53362000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:R30"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4202,6 +4454,7 @@
     <col min="15" max="15" customWidth="1" width="20"/>
     <col min="16" max="16" customWidth="1" width="20"/>
     <col min="17" max="17" customWidth="1" width="20"/>
+    <col min="18" max="18" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4209,51 +4462,54 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2023/3</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>2022/3</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -4267,42 +4523,45 @@
         <v xml:space="preserve">    ESAS FAALİYET GELİRLERİ</v>
       </c>
       <c r="B3">
+        <v>8504289000</v>
+      </c>
+      <c r="C3">
         <v>8772680000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>9574437000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>9784409000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>10817360000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>12237867000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>12809590000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>12493798000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>10577137000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>8670672000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>4798707000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>3432520000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>2429221000</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>772176000</v>
       </c>
     </row>
@@ -4311,42 +4570,45 @@
         <v xml:space="preserve">    Faktoring Gelirleri</v>
       </c>
       <c r="B4">
+        <v>8504289000</v>
+      </c>
+      <c r="C4">
         <v>8772680000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9574437000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>9784409000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>10817360000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>12237867000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>12809590000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>12493798000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>10577137000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>8670672000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>4798707000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>3432520000</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2429221000</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>772176000</v>
       </c>
     </row>
@@ -4364,6 +4626,9 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Finansman Kredilerinden Gelirler</v>
       </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -4373,10 +4638,13 @@
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="H7">
         <v>0</v>
       </c>
       <c r="J7">
@@ -4394,7 +4662,10 @@
       <c r="N7">
         <v>0</v>
       </c>
-      <c r="Q7">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>0</v>
       </c>
     </row>
@@ -4402,6 +4673,9 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Kiralama Gelirleri</v>
       </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
       <c r="C8">
         <v>0</v>
       </c>
@@ -4411,10 +4685,13 @@
       <c r="E8">
         <v>0</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="H8">
         <v>0</v>
       </c>
       <c r="J8">
@@ -4432,7 +4709,10 @@
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="Q8">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>0</v>
       </c>
     </row>
@@ -4458,7 +4738,7 @@
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="H9">
         <v>0</v>
       </c>
       <c r="J9">
@@ -4476,7 +4756,10 @@
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="Q9">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="R9">
         <v>0</v>
       </c>
     </row>
@@ -4485,42 +4768,45 @@
         <v xml:space="preserve">    Finansman Giderleri (-)</v>
       </c>
       <c r="B10">
+        <v>-5204551000</v>
+      </c>
+      <c r="C10">
         <v>-5663917000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-6587793000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-6976006000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-8283697000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-9691056000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-10455033000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-9988153000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-8303811000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-6510345000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-3417399000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>-2431568000</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>-1692690000</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>-603973000</v>
       </c>
     </row>
@@ -4529,42 +4815,45 @@
         <v xml:space="preserve">    BRÜT KAR (ZARAR))</v>
       </c>
       <c r="B11">
+        <v>3299738000</v>
+      </c>
+      <c r="C11">
         <v>3108763000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>2986644000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>2808403000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>2533663000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>2546811000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>2354557000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>2505645000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>2273326000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>2160327000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1381308000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>1000952000</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>736531000</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>168203000</v>
       </c>
     </row>
@@ -4573,42 +4862,45 @@
         <v xml:space="preserve">    Esas Faaliyet Giderleri (-)</v>
       </c>
       <c r="B12">
+        <v>-402023000</v>
+      </c>
+      <c r="C12">
         <v>-367963000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-336575000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-312689000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-286836000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>-249779000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-230783000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-178053000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-156183000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-133733000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-83817000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>-69037000</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>-59165000</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>-31036000</v>
       </c>
     </row>
@@ -4617,42 +4909,45 @@
         <v xml:space="preserve">    BRÜT FAALİYET KARI (ZARARI))</v>
       </c>
       <c r="B13">
+        <v>2897715000</v>
+      </c>
+      <c r="C13">
         <v>2740800000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>2650069000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>2495714000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>2246827000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>2297032000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>2123774000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>2327592000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>2117143000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>2026594000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1297491000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>931915000</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>677366000</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>137167000</v>
       </c>
     </row>
@@ -4661,42 +4956,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B14">
+        <v>3040612000</v>
+      </c>
+      <c r="C14">
         <v>3460924000</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>3497681000</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>3457779000</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>3481737000</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>2426997000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1945553000</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>1581944000</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>2217558000</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1857587000</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1407819000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>883508000</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>1286478000</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>1141711000</v>
       </c>
     </row>
@@ -4705,42 +5003,45 @@
         <v xml:space="preserve">    Karşılık Giderleri</v>
       </c>
       <c r="B15">
+        <v>-70600000</v>
+      </c>
+      <c r="C15">
         <v>-50600000</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-26650000</v>
-      </c>
-      <c r="D15">
-        <v>-53450000</v>
       </c>
       <c r="E15">
         <v>-53450000</v>
       </c>
       <c r="F15">
-        <v>-79615000</v>
+        <v>-53450000</v>
       </c>
       <c r="G15">
         <v>-79615000</v>
       </c>
-      <c r="I15">
+      <c r="H15">
+        <v>-79615000</v>
+      </c>
+      <c r="J15">
         <v>-41863000</v>
-      </c>
-      <c r="J15">
-        <v>-26165000</v>
       </c>
       <c r="K15">
         <v>-26165000</v>
       </c>
       <c r="L15">
+        <v>-26165000</v>
+      </c>
+      <c r="M15">
         <v>-15935000</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>-7369000</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>-7440000</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>-8861000</v>
       </c>
     </row>
@@ -4749,42 +5050,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-2937552000</v>
+      </c>
+      <c r="C16">
         <v>-3347869000</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-3372971000</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-3233613000</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-3226315000</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-2087830000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-1549037000</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-1308119000</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-2021515000</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-1709507000</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-1336356000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>-839478000</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>-1233939000</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>-1109218000</v>
       </c>
     </row>
@@ -4793,42 +5097,45 @@
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B17">
+        <v>2930175000</v>
+      </c>
+      <c r="C17">
         <v>2803255000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>2748129000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>2666430000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>2448799000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>2556584000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>2440675000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>2559554000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>2287021000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>2148509000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>1353019000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>968576000</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>722465000</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>160799000</v>
       </c>
     </row>
@@ -4836,16 +5143,13 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="K18">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
       <c r="L18">
@@ -4857,7 +5161,10 @@
       <c r="N18">
         <v>0</v>
       </c>
-      <c r="Q18">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="R18">
         <v>0</v>
       </c>
     </row>
@@ -4865,16 +5172,13 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar)</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="K19">
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
       <c r="L19">
@@ -4886,7 +5190,10 @@
       <c r="N19">
         <v>0</v>
       </c>
-      <c r="Q19">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="R19">
         <v>0</v>
       </c>
     </row>
@@ -4894,16 +5201,13 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
       <c r="D20">
         <v>0</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="K20">
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>0</v>
       </c>
       <c r="L20">
@@ -4915,7 +5219,10 @@
       <c r="N20">
         <v>0</v>
       </c>
-      <c r="Q20">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="R20">
         <v>0</v>
       </c>
     </row>
@@ -4924,42 +5231,45 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
       <c r="B21">
+        <v>2930175000</v>
+      </c>
+      <c r="C21">
         <v>2803255000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2748129000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>2666430000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>2448799000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>2556584000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2440675000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>2559554000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>2287021000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>2148509000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>1353019000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>968576000</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>722465000</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>160799000</v>
       </c>
     </row>
@@ -4968,42 +5278,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
       <c r="B22">
+        <v>-877868000</v>
+      </c>
+      <c r="C22">
         <v>-839829000</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-823271000</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-798845000</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-735768000</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>-768153000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-733496000</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>-810476000</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>-703925000</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>-643773000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-334883000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>-211813000</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>-175745000</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>-44513000</v>
       </c>
     </row>
@@ -5012,42 +5325,45 @@
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
       <c r="B23">
+        <v>-900620000</v>
+      </c>
+      <c r="C23">
         <v>-856378000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-832326000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-815901000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-752884000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>-785295000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-750535000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-812737000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>-705857000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>-646026000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-335593000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>-212616000</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>-125516000</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>-96064000</v>
       </c>
     </row>
@@ -5073,21 +5389,24 @@
         <v>0</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>18000</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>26000</v>
+      <c r="H25">
+        <v>0</v>
       </c>
       <c r="M25">
         <v>26000</v>
       </c>
       <c r="N25">
+        <v>26000</v>
+      </c>
+      <c r="O25">
         <v>-50229000</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>0</v>
       </c>
     </row>
@@ -5096,42 +5415,45 @@
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
       <c r="B26">
+        <v>2052307000</v>
+      </c>
+      <c r="C26">
         <v>1963426000</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>1924858000</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1867585000</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>1713031000</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1788431000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>1707179000</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>1749078000</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>1583096000</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>1504736000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>1018136000</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>756763000</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>546720000</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>116286000</v>
       </c>
     </row>
@@ -5139,16 +5461,19 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Net Karı (Zararı)</v>
       </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="K27">
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>0</v>
       </c>
       <c r="L27">
@@ -5160,7 +5485,10 @@
       <c r="N27">
         <v>0</v>
       </c>
-      <c r="Q27">
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="R27">
         <v>0</v>
       </c>
     </row>
@@ -5169,42 +5497,45 @@
         <v xml:space="preserve">    DÖNEM KARI (ZARARI)</v>
       </c>
       <c r="B28">
+        <v>2052307000</v>
+      </c>
+      <c r="C28">
         <v>1963426000</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1924858000</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>1867585000</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>1713031000</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>1788431000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>1707179000</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1749078000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>1583096000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>1504736000</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>1018136000</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>756763000</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>546720000</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>116286000</v>
       </c>
     </row>
@@ -5221,10 +5552,10 @@
       <c r="D29">
         <v>0</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="K29">
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>0</v>
       </c>
       <c r="L29">
@@ -5236,7 +5567,10 @@
       <c r="N29">
         <v>0</v>
       </c>
-      <c r="Q29">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="R29">
         <v>0</v>
       </c>
     </row>
@@ -5245,55 +5579,58 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B30">
+        <v>2052307000</v>
+      </c>
+      <c r="C30">
         <v>1963426000</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1924858000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1867585000</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>1713031000</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>1788431000</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1707179000</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1749078000</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1583096000</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>1504736000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>1018136000</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>756763000</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>546720000</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>116286000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5309,6 +5646,7 @@
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
     <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5316,42 +5654,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -5365,42 +5706,45 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>443073000</v>
+      </c>
+      <c r="C3">
         <v>-179034000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>2180215000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>621040000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>490067000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>-451646000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1115003000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1463179000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>2203262000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1881309000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>945675000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>263233000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>-112745000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>187010000</v>
       </c>
     </row>
@@ -5409,42 +5753,45 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>3523540000</v>
+      </c>
+      <c r="C4">
         <v>1637061000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9565696000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>6763998000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>4622136000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>1952588000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>12952560000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>10134816000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>6793144000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>6814870000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>2727731000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2226469000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>718367000</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>570734000</v>
       </c>
     </row>
@@ -5453,42 +5800,45 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-2478008000</v>
+      </c>
+      <c r="C5">
         <v>-1525646000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-6282796000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>-5346945000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>-3617110000</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>-2352937000</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>-10948614000</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>-8006534000</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>-4203467000</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>-5474956000</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>-1994450000</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>-1588750000</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>-563308000</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>-515777000</v>
       </c>
     </row>
@@ -5499,16 +5849,22 @@
       <c r="B6">
         <v>0</v>
       </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="G6">
         <v>0</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="N6">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>0</v>
       </c>
     </row>
@@ -5517,42 +5873,45 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>9352000</v>
+      </c>
+      <c r="C7">
         <v>2164000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>10829000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>8916000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>6074000</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>2545000</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>21825000</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>17987000</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>11284000</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1164455000</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>410691000</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>21394000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>3653000</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>2811000</v>
       </c>
     </row>
@@ -5561,42 +5920,45 @@
         <v xml:space="preserve">    Zarar Olarak Muhasebeleştirilen Takipteki Alacaklardan Tahsilatlar</v>
       </c>
       <c r="B8">
+        <v>492000</v>
+      </c>
+      <c r="C8">
         <v>84000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>444000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>349000</v>
-      </c>
-      <c r="E8">
-        <v>213000</v>
       </c>
       <c r="F8">
         <v>213000</v>
       </c>
       <c r="G8">
+        <v>213000</v>
+      </c>
+      <c r="H8">
         <v>1264000</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>948000</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>465000</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>-5619000</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>1643000</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>-7088000</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>4176000</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>6641000</v>
       </c>
     </row>
@@ -5605,42 +5967,45 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-140347000</v>
+      </c>
+      <c r="C9">
         <v>-60360000</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-195929000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>-146095000</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>-96959000</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>-43874000</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-137475000</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>-101599000</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>-66213000</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>-68722000</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>-27669000</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>-31141000</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>-16511000</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>-31036000</v>
       </c>
     </row>
@@ -5649,42 +6014,45 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-433836000</v>
+      </c>
+      <c r="C10">
         <v>-224950000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-814443000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-596191000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-388758000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-2314000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-722637000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-555957000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-326100000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-539203000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-159446000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-116124000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>-62954000</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>-33110000</v>
       </c>
     </row>
@@ -5693,42 +6061,45 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-38120000</v>
+      </c>
+      <c r="C11">
         <v>-7387000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-103586000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>-62992000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>-35529000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>-7867000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>-51920000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>-26482000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>-5851000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>-9516000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>-12825000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>-241527000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>-196168000</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>179882000</v>
       </c>
     </row>
@@ -5737,42 +6108,45 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>187309000</v>
+      </c>
+      <c r="C12">
         <v>360276000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-3138957000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-1153976000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-1052033000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>643923000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-1420185000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-1062274000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-1852227000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-2181983000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>821579000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-872395000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>376075000</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>-172940000</v>
       </c>
     </row>
@@ -5781,42 +6155,45 @@
         <v xml:space="preserve">    Faktoring Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B13">
+        <v>-3975675000</v>
+      </c>
+      <c r="C13">
         <v>7111471000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>-9201164000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>3177057000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>928345000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>12279739000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>5197100000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>10893193000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>-1332376000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>-14097533000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>-2473656000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>-15425263000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>-2130551000</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>-1096481000</v>
       </c>
     </row>
@@ -5827,13 +6204,19 @@
       <c r="B14">
         <v>0</v>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="N14">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>0</v>
       </c>
     </row>
@@ -5844,13 +6227,19 @@
       <c r="B15">
         <v>0</v>
       </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="N15">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>0</v>
       </c>
     </row>
@@ -5861,13 +6250,19 @@
       <c r="B16">
         <v>0</v>
       </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="N16">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>0</v>
       </c>
     </row>
@@ -5876,42 +6271,45 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-43991000</v>
+      </c>
+      <c r="C17">
         <v>-24817000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>5973000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>7357000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-1325000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>-2948000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>89016000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>104274000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>48497000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>-12339000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>-235129000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>-138698000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>12202000</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>-58717000</v>
       </c>
     </row>
@@ -5920,42 +6318,45 @@
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
       <c r="B18">
+        <v>12954000</v>
+      </c>
+      <c r="C18">
         <v>2120000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-365000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>5589000</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>-366000</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>9873000</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>286000</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>-90000</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>2052000</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>-5378000</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>-3513000</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>-1841000</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>-6824000</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>6637000</v>
       </c>
     </row>
@@ -5966,13 +6367,19 @@
       <c r="B19">
         <v>0</v>
       </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="N19">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>0</v>
       </c>
     </row>
@@ -5981,42 +6388,45 @@
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B20">
+        <v>-1393000</v>
+      </c>
+      <c r="C20">
         <v>-3169000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-7712000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-4552000</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-2881000</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>-334000</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>11497000</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>11662000</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>10746000</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>5607000</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>-351000</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>-1471000</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>-802000</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>242000</v>
       </c>
     </row>
@@ -6025,42 +6435,45 @@
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
       <c r="B21">
+        <v>4138763000</v>
+      </c>
+      <c r="C21">
         <v>-6755274000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>6052733000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>-4331381000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>-1946339000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>-11696944000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>-6699356000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>-12088837000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>-556218000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>11909592000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>2945411000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>14632789000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>2554514000</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>899872000</v>
       </c>
     </row>
@@ -6071,13 +6484,19 @@
       <c r="B22">
         <v>0</v>
       </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="N22">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>0</v>
       </c>
     </row>
@@ -6086,42 +6505,45 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>56651000</v>
+      </c>
+      <c r="C23">
         <v>29945000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>11578000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-8046000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-29467000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>54537000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-18728000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>17524000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-24928000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>18068000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>588817000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>62089000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>-52464000</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>75507000</v>
       </c>
     </row>
@@ -6130,42 +6552,45 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>630382000</v>
+      </c>
+      <c r="C24">
         <v>181242000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-958742000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-532936000</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>-561966000</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>192277000</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-305182000</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>400905000</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>351035000</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>-300674000</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>1767254000</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>-609162000</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>263330000</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>14070000</v>
       </c>
     </row>
@@ -6176,13 +6601,19 @@
       <c r="B25">
         <v>0</v>
       </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="N25">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>0</v>
       </c>
     </row>
@@ -6196,42 +6627,45 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-7006000</v>
+      </c>
+      <c r="C27">
         <v>-1420000</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-3991000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>-3347000</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>-2115000</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>-2015000</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>-5419000</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>-16666000</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>-13867000</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>-8079000</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>-304000</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>-4121000</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>-491000</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>-1894000</v>
       </c>
     </row>
@@ -6243,10 +6677,10 @@
         <v>0</v>
       </c>
       <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
         <v>239000</v>
-      </c>
-      <c r="D28">
-        <v>230000</v>
       </c>
       <c r="E28">
         <v>230000</v>
@@ -6254,19 +6688,22 @@
       <c r="F28">
         <v>230000</v>
       </c>
-      <c r="J28">
+      <c r="G28">
+        <v>230000</v>
+      </c>
+      <c r="K28">
         <v>826000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>91000</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
       <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
         <v>81000</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>120000</v>
       </c>
     </row>
@@ -6277,13 +6714,19 @@
       <c r="B29">
         <v>0</v>
       </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="N29">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>0</v>
       </c>
     </row>
@@ -6299,13 +6742,19 @@
       <c r="B31">
         <v>0</v>
       </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="N31">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="O31">
         <v>0</v>
       </c>
     </row>
@@ -6321,13 +6770,19 @@
       <c r="B33">
         <v>0</v>
       </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
       <c r="F33">
         <v>0</v>
       </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="N33">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="O33">
         <v>-1736000</v>
       </c>
     </row>
@@ -6336,42 +6791,45 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-7006000</v>
+      </c>
+      <c r="C34">
         <v>-1420000</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>53051000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>16883000</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>-1885000</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>-1785000</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>-5419000</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>-16666000</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>-13867000</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>-7253000</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>-213000</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>-4121000</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>-410000</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>-3510000</v>
       </c>
     </row>
@@ -6388,36 +6846,42 @@
         <v>0</v>
       </c>
       <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
         <v>-640415000</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-237548000</v>
       </c>
       <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
         <v>-289990000</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
       <c r="H36">
-        <v>-105628000</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>-105628000</v>
       </c>
       <c r="J36">
+        <v>-105628000</v>
+      </c>
+      <c r="K36">
         <v>-1513520000</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>-618627000</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>-767915000</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>581475000</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>-1957932000</v>
       </c>
     </row>
@@ -6433,10 +6897,16 @@
       <c r="B38">
         <v>0</v>
       </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="N38">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="O38">
         <v>0</v>
       </c>
     </row>
@@ -6447,10 +6917,16 @@
       <c r="B39">
         <v>0</v>
       </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="N39">
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="O39">
         <v>-1766000</v>
       </c>
     </row>
@@ -6458,10 +6934,16 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="N40">
+      <c r="B40">
+        <v>-197000</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>0</v>
       </c>
     </row>
@@ -6470,42 +6952,45 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>-93916000</v>
+      </c>
+      <c r="C41">
         <v>-93917000</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>693010000</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>402867000</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>640415000</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>-289990000</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>105628000</v>
-      </c>
-      <c r="H41">
-        <v>-105628000</v>
       </c>
       <c r="I41">
         <v>-105628000</v>
       </c>
       <c r="J41">
+        <v>-105628000</v>
+      </c>
+      <c r="K41">
         <v>611665000</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>-163639000</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>684285000</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>-186440000</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>-8560000</v>
       </c>
     </row>
@@ -6514,42 +6999,45 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
       <c r="B42">
+        <v>2823000</v>
+      </c>
+      <c r="C42">
         <v>1030000</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>3697000</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>3910000</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>1093000</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>1754000</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>2433000</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>2751000</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>1768000</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>30371000</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>11201000</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>8608000</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>23655000</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>14140000</v>
       </c>
     </row>
@@ -6558,42 +7046,45 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>532283000</v>
+      </c>
+      <c r="C43">
         <v>86935000</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-208984000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>-109276000</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>77657000</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>-97744000</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>-202540000</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>281362000</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>233308000</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>334109000</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>1614603000</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>79610000</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>100135000</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>16140000</v>
       </c>
     </row>
@@ -6609,14 +7100,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6632,6 +7123,7 @@
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
     <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6639,42 +7131,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -6688,24 +7183,27 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>622107000</v>
+      </c>
+      <c r="C3">
         <v>-179034000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1559175000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>130973000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>941713000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>-451646000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>-348176000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>-740083000</v>
       </c>
     </row>
@@ -6714,24 +7212,27 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>1886479000</v>
+      </c>
+      <c r="C4">
         <v>1637061000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2801698000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2141862000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2669548000</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>1952588000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2817744000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>3341672000</v>
       </c>
     </row>
@@ -6740,24 +7241,27 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-952362000</v>
+      </c>
+      <c r="C5">
         <v>-1525646000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-935851000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>-1729835000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>-1264173000</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>-2352937000</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>-2942080000</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>-3803067000</v>
       </c>
     </row>
@@ -6768,7 +7272,13 @@
       <c r="B6">
         <v>0</v>
       </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>0</v>
       </c>
     </row>
@@ -6777,24 +7287,27 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>7188000</v>
+      </c>
+      <c r="C7">
         <v>2164000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>1913000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2842000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>3529000</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>2545000</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>3838000</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>6703000</v>
       </c>
     </row>
@@ -6803,24 +7316,27 @@
         <v xml:space="preserve">    Zarar Olarak Muhasebeleştirilen Takipteki Alacaklardan Tahsilatlar</v>
       </c>
       <c r="B8">
+        <v>408000</v>
+      </c>
+      <c r="C8">
         <v>84000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>95000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>136000</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>213000</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>316000</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>483000</v>
       </c>
     </row>
@@ -6829,24 +7345,27 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-79987000</v>
+      </c>
+      <c r="C9">
         <v>-60360000</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-49834000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>-49136000</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>-53085000</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>-43874000</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-35876000</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>-35386000</v>
       </c>
     </row>
@@ -6855,24 +7374,27 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-208886000</v>
+      </c>
+      <c r="C10">
         <v>-224950000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-218252000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-207433000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-386444000</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>-2314000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-166680000</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-229857000</v>
       </c>
     </row>
@@ -6881,24 +7403,27 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-30733000</v>
+      </c>
+      <c r="C11">
         <v>-7387000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-40594000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>-27463000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>-27662000</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>-7867000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>-25438000</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>-20631000</v>
       </c>
     </row>
@@ -6907,24 +7432,27 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>-172967000</v>
+      </c>
+      <c r="C12">
         <v>360276000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-1984981000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-101943000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-1695956000</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>643923000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-357911000</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>789953000</v>
       </c>
     </row>
@@ -6933,24 +7461,27 @@
         <v xml:space="preserve">    Faktoring Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B13">
+        <v>-11087146000</v>
+      </c>
+      <c r="C13">
         <v>7111471000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>-12378221000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>2248712000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>-11351394000</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>12279739000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>-5696093000</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>12225569000</v>
       </c>
     </row>
@@ -6961,7 +7492,13 @@
       <c r="B14">
         <v>0</v>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>0</v>
       </c>
     </row>
@@ -6972,7 +7509,13 @@
       <c r="B15">
         <v>0</v>
       </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>0</v>
       </c>
     </row>
@@ -6983,7 +7526,13 @@
       <c r="B16">
         <v>0</v>
       </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>0</v>
       </c>
     </row>
@@ -6992,24 +7541,27 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-19174000</v>
+      </c>
+      <c r="C17">
         <v>-24817000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-1384000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>8682000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>1623000</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>-2948000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-15258000</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>55777000</v>
       </c>
     </row>
@@ -7018,24 +7570,27 @@
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
       <c r="B18">
+        <v>10834000</v>
+      </c>
+      <c r="C18">
         <v>2120000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-5954000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>5955000</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>-10239000</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>9873000</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>376000</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>-2142000</v>
       </c>
     </row>
@@ -7046,7 +7601,13 @@
       <c r="B19">
         <v>0</v>
       </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>0</v>
       </c>
     </row>
@@ -7055,24 +7616,27 @@
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B20">
+        <v>1776000</v>
+      </c>
+      <c r="C20">
         <v>-3169000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-3160000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-1671000</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-2547000</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>-334000</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>-165000</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>916000</v>
       </c>
     </row>
@@ -7081,24 +7645,27 @@
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
       <c r="B21">
+        <v>10894037000</v>
+      </c>
+      <c r="C21">
         <v>-6755274000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>10384114000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>-2385042000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>9750605000</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>-11696944000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>5389481000</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>-11532619000</v>
       </c>
     </row>
@@ -7109,7 +7676,13 @@
       <c r="B22">
         <v>0</v>
       </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>0</v>
       </c>
     </row>
@@ -7118,24 +7691,27 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>26706000</v>
+      </c>
+      <c r="C23">
         <v>29945000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>19624000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>21421000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-84004000</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>54537000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-36252000</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>42452000</v>
       </c>
     </row>
@@ -7144,24 +7720,27 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>449140000</v>
+      </c>
+      <c r="C24">
         <v>181242000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-425806000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>29030000</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>-754243000</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>192277000</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-706087000</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>49870000</v>
       </c>
     </row>
@@ -7172,7 +7751,13 @@
       <c r="B25">
         <v>0</v>
       </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
@@ -7186,24 +7771,27 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-5586000</v>
+      </c>
+      <c r="C27">
         <v>-1420000</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-644000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>-1232000</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>-100000</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>-2015000</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>11247000</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>-2799000</v>
       </c>
     </row>
@@ -7215,15 +7803,18 @@
         <v>0</v>
       </c>
       <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
         <v>9000</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>230000</v>
       </c>
     </row>
@@ -7234,7 +7825,13 @@
       <c r="B29">
         <v>0</v>
       </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
       <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>0</v>
       </c>
     </row>
@@ -7250,7 +7847,13 @@
       <c r="B31">
         <v>0</v>
       </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>0</v>
       </c>
     </row>
@@ -7266,7 +7869,13 @@
       <c r="B33">
         <v>0</v>
       </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
       <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
         <v>0</v>
       </c>
     </row>
@@ -7275,24 +7884,27 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>-5586000</v>
+      </c>
+      <c r="C34">
         <v>-1420000</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>36168000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>18768000</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>-100000</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>-1785000</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>11247000</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>-2799000</v>
       </c>
     </row>
@@ -7309,15 +7921,24 @@
         <v>0</v>
       </c>
       <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
         <v>-402867000</v>
       </c>
+      <c r="E36">
+        <v>-237548000</v>
+      </c>
       <c r="F36">
+        <v>289990000</v>
+      </c>
+      <c r="G36">
         <v>-289990000</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>105628000</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>0</v>
       </c>
     </row>
@@ -7333,6 +7954,9 @@
       <c r="B38">
         <v>0</v>
       </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -7341,6 +7965,9 @@
       <c r="B39">
         <v>0</v>
       </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -7352,24 +7979,27 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>1000</v>
+      </c>
+      <c r="C41">
         <v>-93917000</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>290143000</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>-237548000</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>930405000</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>-289990000</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>211256000</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>0</v>
       </c>
     </row>
@@ -7378,24 +8008,27 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
       <c r="B42">
+        <v>1793000</v>
+      </c>
+      <c r="C42">
         <v>1030000</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-213000</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>2817000</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>-661000</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>1754000</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>-318000</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>983000</v>
       </c>
     </row>
@@ -7404,24 +8037,27 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>445348000</v>
+      </c>
+      <c r="C43">
         <v>86935000</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-99708000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>-186933000</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>175401000</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>-97744000</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>-483902000</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>48054000</v>
       </c>
     </row>
@@ -7437,14 +8073,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -7460,6 +8096,7 @@
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
     <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7467,42 +8104,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2023/6</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>2022/6</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -7516,33 +8156,36 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM ÖNCESİ FAALİYET KARI (ZARARI)</v>
       </c>
       <c r="B3">
+        <v>2133221000</v>
+      </c>
+      <c r="C3">
         <v>2452827000</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>2180215000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>272864000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>-598192000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1115003000</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3138896000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1881309000</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1321653000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>263233000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>187010000</v>
       </c>
     </row>
@@ -7551,33 +8194,36 @@
         <v xml:space="preserve">    Alınan Faizler/ Alınan Kâr Payları / Kiralama Gelirleri</v>
       </c>
       <c r="B4">
+        <v>8467100000</v>
+      </c>
+      <c r="C4">
         <v>9250169000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>9565696000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>9581742000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>10781552000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>12952560000</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>10880283000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>6814870000</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>4235833000</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2226469000</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>570734000</v>
       </c>
     </row>
@@ -7586,33 +8232,36 @@
         <v xml:space="preserve">    Ödenen Faizler / Ödenen Kâr Payları / Kiralama Giderleri</v>
       </c>
       <c r="B5">
+        <v>-5143694000</v>
+      </c>
+      <c r="C5">
         <v>-5455505000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-6282796000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>-8289025000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>-10362257000</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>-10948614000</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>-7683973000</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>-5474956000</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>-3019892000</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>-1588750000</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>-515777000</v>
       </c>
     </row>
@@ -7620,10 +8269,10 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="N6">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>0</v>
       </c>
     </row>
@@ -7632,33 +8281,36 @@
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
       <c r="B7">
+        <v>14107000</v>
+      </c>
+      <c r="C7">
         <v>10448000</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>10829000</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>12754000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>16615000</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>21825000</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>765048000</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1164455000</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>428432000</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>21394000</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>2811000</v>
       </c>
     </row>
@@ -7667,33 +8319,36 @@
         <v xml:space="preserve">    Zarar Olarak Muhasebeleştirilen Takipteki Alacaklardan Tahsilatlar</v>
       </c>
       <c r="B8">
+        <v>723000</v>
+      </c>
+      <c r="C8">
         <v>315000</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>444000</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>665000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>1012000</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1264000</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>-6797000</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>-5619000</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>-9621000</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>-7088000</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>6641000</v>
       </c>
     </row>
@@ -7702,33 +8357,36 @@
         <v xml:space="preserve">    Personele ve Hizmet Tedarik Edenlere Yapılan Nakit Ödemeler</v>
       </c>
       <c r="B9">
+        <v>-239317000</v>
+      </c>
+      <c r="C9">
         <v>-212415000</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-195929000</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>-181971000</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>-168221000</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-137475000</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>-107266000</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>-68722000</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>-42299000</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>-31141000</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>-31036000</v>
       </c>
     </row>
@@ -7737,33 +8395,36 @@
         <v xml:space="preserve">    Ödenen Vergiler</v>
       </c>
       <c r="B10">
+        <v>-859521000</v>
+      </c>
+      <c r="C10">
         <v>-1037079000</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-814443000</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>-762871000</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-785295000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-722637000</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-705857000</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>-539203000</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>-212616000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-116124000</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>-33110000</v>
       </c>
     </row>
@@ -7772,33 +8433,36 @@
         <v xml:space="preserve">    Diğer</v>
       </c>
       <c r="B11">
+        <v>-106177000</v>
+      </c>
+      <c r="C11">
         <v>-103106000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-103586000</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>-88430000</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>-81598000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>-51920000</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>-2542000</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>-9516000</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>-58184000</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>-241527000</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>179882000</v>
       </c>
     </row>
@@ -7807,33 +8471,36 @@
         <v xml:space="preserve">    ESAS FAALİYET KONUSU VARLIK VE YÜKÜMLÜLÜKLERDEKİ DEĞİŞİM</v>
       </c>
       <c r="B12">
+        <v>-1899615000</v>
+      </c>
+      <c r="C12">
         <v>-3422604000</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-3138957000</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-1511887000</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-619991000</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-1420185000</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-4855789000</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>-2181983000</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-426891000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-872395000</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>-172940000</v>
       </c>
     </row>
@@ -7842,33 +8509,36 @@
         <v xml:space="preserve">    Faktoring Alacaklarındaki Net (Artış) Azalış</v>
       </c>
       <c r="B13">
+        <v>-14105184000</v>
+      </c>
+      <c r="C13">
         <v>-14369432000</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>-9201164000</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>-2519036000</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>7457821000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>5197100000</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>-12956253000</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>-14097533000</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>-15768368000</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>-15425263000</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>-1096481000</v>
       </c>
     </row>
@@ -7876,10 +8546,10 @@
       <c r="A14" t="str">
         <v xml:space="preserve">    Finansman Kredilerindeki Net (Artış) Azalış</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="N14">
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>0</v>
       </c>
     </row>
@@ -7887,10 +8557,10 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Alacaklarda Net (Artış) Azalış</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="N15">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>0</v>
       </c>
     </row>
@@ -7898,10 +8568,10 @@
       <c r="A16" t="str">
         <v xml:space="preserve">    Tasarruf Finansman Alacaklarındaki Net (Artış) Azalış</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="N16">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>0</v>
       </c>
     </row>
@@ -7910,33 +8580,36 @@
         <v xml:space="preserve">    Diğer Varlıklarda Net (Artış) Azalış</v>
       </c>
       <c r="B17">
+        <v>-36693000</v>
+      </c>
+      <c r="C17">
         <v>-15896000</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>5973000</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-7901000</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>39194000</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>89016000</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>271287000</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>-12339000</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>-386029000</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>-138698000</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>-58717000</v>
       </c>
     </row>
@@ -7945,33 +8618,36 @@
         <v xml:space="preserve">    Faktoring Borçlarındaki Net Artış (Azalış)</v>
       </c>
       <c r="B18">
+        <v>12955000</v>
+      </c>
+      <c r="C18">
         <v>-8118000</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-365000</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>5965000</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>-2132000</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>286000</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>187000</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>-5378000</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>1470000</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>-1841000</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>6637000</v>
       </c>
     </row>
@@ -7979,10 +8655,10 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Tasarruf Fon Havuzundaki Net Artış (Azalış)</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="N19">
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>0</v>
       </c>
     </row>
@@ -7991,33 +8667,36 @@
         <v xml:space="preserve">    Kiralama İşlemlerinden Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B20">
+        <v>-6224000</v>
+      </c>
+      <c r="C20">
         <v>-10547000</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-7712000</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-4717000</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-2130000</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>11497000</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>16704000</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>5607000</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>-1020000</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>-1471000</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>242000</v>
       </c>
     </row>
@@ -8026,33 +8705,36 @@
         <v xml:space="preserve">    Alınan Kredilerdeki Net Artış (Azalış)</v>
       </c>
       <c r="B21">
+        <v>12137835000</v>
+      </c>
+      <c r="C21">
         <v>10994403000</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>6052733000</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1058100000</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>-8089477000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>-6699356000</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>8407963000</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>11909592000</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>15023686000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>14632789000</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>899872000</v>
       </c>
     </row>
@@ -8060,10 +8742,10 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Vadesi Gelmiş Borçlarda Net Artış (Azalış)</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="N22">
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>0</v>
       </c>
     </row>
@@ -8072,33 +8754,36 @@
         <v xml:space="preserve">    Diğer Borçlarda Net Artış (Azalış)</v>
       </c>
       <c r="B23">
+        <v>97696000</v>
+      </c>
+      <c r="C23">
         <v>-13014000</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>11578000</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>-44298000</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-23267000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-18728000</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>-595677000</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>18068000</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>703370000</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>62089000</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>75507000</v>
       </c>
     </row>
@@ -8107,33 +8792,36 @@
         <v xml:space="preserve">    ESAS FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞI</v>
       </c>
       <c r="B24">
+        <v>233606000</v>
+      </c>
+      <c r="C24">
         <v>-969777000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-958742000</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>-1239023000</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>-1218183000</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-305182000</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>-1716893000</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>-300674000</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>894762000</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>-609162000</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>14070000</v>
       </c>
     </row>
@@ -8141,10 +8829,10 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    İktisap Edilen İştirakler, Bağlı Ortaklıklar ve Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları)</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="N25">
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>0</v>
       </c>
     </row>
@@ -8158,33 +8846,36 @@
         <v xml:space="preserve">    Satın Alınan Menkuller ve Gayrimenkuller</v>
       </c>
       <c r="B27">
+        <v>-8882000</v>
+      </c>
+      <c r="C27">
         <v>-3396000</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-3991000</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>7900000</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>6333000</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>-5419000</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>-21642000</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>-8079000</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>-3934000</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>-4121000</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>-1894000</v>
       </c>
     </row>
@@ -8196,18 +8887,21 @@
         <v>9000</v>
       </c>
       <c r="C28">
+        <v>9000</v>
+      </c>
+      <c r="D28">
         <v>239000</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>826000</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>10000</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="N28">
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>120000</v>
       </c>
     </row>
@@ -8215,10 +8909,10 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Elde Edilen Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıklar</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="N29">
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>0</v>
       </c>
     </row>
@@ -8231,10 +8925,10 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Satın Alınan İtfa Edilmiş Maliyeti ile Ölçülen Finansal Varlıklar</v>
       </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="N31">
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="O31">
         <v>0</v>
       </c>
     </row>
@@ -8247,10 +8941,10 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="N33">
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="O33">
         <v>-1736000</v>
       </c>
     </row>
@@ -8259,33 +8953,36 @@
         <v xml:space="preserve">    YATIRIM FAALİYETLERİNDEN KAYNAKLANAN NET NAKİT AKIŞLARI</v>
       </c>
       <c r="B34">
+        <v>47930000</v>
+      </c>
+      <c r="C34">
         <v>53416000</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>53051000</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>28130000</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>6563000</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>-5419000</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>-20907000</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>-7253000</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>-3924000</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>-4121000</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>-3510000</v>
       </c>
     </row>
@@ -8299,30 +8996,36 @@
         <v xml:space="preserve">    Krediler ve İhraç Edilen Menkul Değerlerden Kaynaklanan Nakit Çıkışı</v>
       </c>
       <c r="B36">
+        <v>-640415000</v>
+      </c>
+      <c r="C36">
         <v>-350425000</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-640415000</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-131920000</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="I36">
+      <c r="F36">
+        <v>105628000</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="J36">
         <v>-1000521000</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>-1513520000</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>-1968017000</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>-767915000</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>-1957932000</v>
       </c>
     </row>
@@ -8335,10 +9038,10 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Temettü Ödemeleri</v>
       </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="N38">
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="O38">
         <v>0</v>
       </c>
     </row>
@@ -8346,10 +9049,10 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Kiralamaya İlişkin Ödemeler</v>
       </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="N39">
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="O39">
         <v>-1766000</v>
       </c>
     </row>
@@ -8357,10 +9060,10 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Diğer</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="N40">
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>0</v>
       </c>
     </row>
@@ -8369,33 +9072,36 @@
         <v xml:space="preserve">    FİNANSMAN FAALİYETLERİNDEN SAĞLANAN NET NAKİT</v>
       </c>
       <c r="B41">
+        <v>-41321000</v>
+      </c>
+      <c r="C41">
         <v>889083000</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>693010000</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>614123000</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>851671000</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>105628000</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>669676000</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>611665000</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>707086000</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>684285000</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>-8560000</v>
       </c>
     </row>
@@ -8404,33 +9110,36 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakde Eşdeğer Varlıklar Üzerindeki Etkisi</v>
       </c>
       <c r="B42">
+        <v>5427000</v>
+      </c>
+      <c r="C42">
         <v>2973000</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>3697000</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>3592000</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>1758000</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>2433000</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>20938000</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>30371000</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>-3846000</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>8608000</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>14140000</v>
       </c>
     </row>
@@ -8439,33 +9148,36 @@
         <v xml:space="preserve">    NAKİT VE NAKDE EŞDEĞER VARLIKLARDAKİ NET ARTIŞ (AZALIŞ)</v>
       </c>
       <c r="B43">
+        <v>245642000</v>
+      </c>
+      <c r="C43">
         <v>-24305000</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-208984000</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>-593178000</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>-358191000</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>-202540000</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>-1047186000</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>334109000</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>1594078000</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>79610000</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>16140000</v>
       </c>
     </row>
@@ -8481,7 +9193,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
   </ignoredErrors>
 </worksheet>
 </file>